--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 전투 데이터 테이블 V5.0.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 전투 데이터 테이블 V5.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\개인\게임인재원 7기\Hero Influence\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HeroInfluencetmp\Assets\_ProtoType_Merge\ASB\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D12D85A-07F4-43EC-A1F2-881D8192B47D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670C6A44-390B-44C2-A156-FBAA5F9886F0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="759" xr2:uid="{B7614390-11AA-4CA0-8D0B-42C45BC335B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="759" activeTab="4" xr2:uid="{B7614390-11AA-4CA0-8D0B-42C45BC335B4}"/>
   </bookViews>
   <sheets>
     <sheet name="문서 개요" sheetId="7" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="878">
   <si>
     <t>공격력</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -3570,6 +3570,46 @@
   </si>
   <si>
     <t>BonusDEF Lv○</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>#name</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>#type</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>percent</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">int </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>#data</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>#end</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3983,7 +4023,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4377,6 +4417,27 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4384,9 +4445,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4411,21 +4469,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5001,437 +5044,438 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBBD2113-028D-4F5A-981F-5AF98CC66DCF}">
-  <dimension ref="A2:F37"/>
-  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <dimension ref="B2:G37"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.5625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.0625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.3125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.1875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.5625" style="1"/>
+    <col min="1" max="1" width="8.58203125" style="1"/>
+    <col min="2" max="2" width="5.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.58203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="34.9" x14ac:dyDescent="0.6">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="2:7" ht="36" x14ac:dyDescent="0.45">
+      <c r="B2" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="B2" s="14"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="B4" s="12" t="s">
+      <c r="C2" s="14"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C4" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="D4" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="B5" s="13">
+    <row r="5" spans="2:7" ht="34" x14ac:dyDescent="0.45">
+      <c r="C5" s="13">
         <v>46108</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="F5" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="13"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="B6" s="13">
+      <c r="G5" s="13"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C6" s="13">
         <v>46114</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="D6" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="E6" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="F6" s="13"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="B7" s="13">
+      <c r="G6" s="13"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C7" s="13">
         <v>46115</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="D7" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" spans="1:6" ht="67.5" x14ac:dyDescent="0.6">
-      <c r="B8" s="13">
+      <c r="G7" s="13"/>
+    </row>
+    <row r="8" spans="2:7" ht="68" x14ac:dyDescent="0.45">
+      <c r="C8" s="13">
         <v>46119</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="D8" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="F8" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="F8" s="13"/>
-    </row>
-    <row r="9" spans="1:6" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="B9" s="13">
+      <c r="G8" s="13"/>
+    </row>
+    <row r="9" spans="2:7" ht="34" x14ac:dyDescent="0.45">
+      <c r="C9" s="13">
         <v>46120</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="D9" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="F9" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:6" ht="50.65" x14ac:dyDescent="0.6">
-      <c r="B10" s="13">
+      <c r="G9" s="13"/>
+    </row>
+    <row r="10" spans="2:7" ht="51" x14ac:dyDescent="0.45">
+      <c r="C10" s="13">
         <v>46121</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="D10" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="E10" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="F10" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="B11" s="13">
+      <c r="G10" s="13"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C11" s="13">
         <v>46125</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="F11" s="15" t="s">
         <v>520</v>
       </c>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" spans="1:6" ht="118.15" x14ac:dyDescent="0.6">
-      <c r="B12" s="13">
+      <c r="G11" s="13"/>
+    </row>
+    <row r="12" spans="2:7" ht="119" x14ac:dyDescent="0.45">
+      <c r="C12" s="13">
         <v>46132</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="D12" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="E12" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="F12" s="15" t="s">
         <v>521</v>
       </c>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="B13" s="13">
+      <c r="G12" s="13"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C13" s="13">
         <v>46133</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="13" t="s">
         <v>490</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="F13" s="15" t="s">
         <v>491</v>
       </c>
-      <c r="F13" s="13"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="B14" s="13">
+      <c r="G13" s="13"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C14" s="13">
         <v>46133</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
         <v>495</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="F14" s="15" t="s">
         <v>508</v>
       </c>
-      <c r="F14" s="13"/>
-    </row>
-    <row r="15" spans="1:6" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="B15" s="13">
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" spans="2:7" ht="34" x14ac:dyDescent="0.45">
+      <c r="C15" s="13">
         <v>46141</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="D15" s="13" t="s">
         <v>555</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>584</v>
       </c>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="1:6" ht="67.5" x14ac:dyDescent="0.6">
-      <c r="B16" s="13">
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" spans="2:7" ht="68" x14ac:dyDescent="0.45">
+      <c r="C16" s="13">
         <v>46149</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="D16" s="13" t="s">
         <v>607</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="E16" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>703</v>
       </c>
-      <c r="F16" s="13"/>
-    </row>
-    <row r="17" spans="1:6" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="B17" s="13">
+      <c r="G16" s="13"/>
+    </row>
+    <row r="17" spans="2:7" ht="34" x14ac:dyDescent="0.45">
+      <c r="C17" s="13">
         <v>46150</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="D17" s="13" t="s">
         <v>716</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="E17" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="F17" s="15" t="s">
         <v>717</v>
       </c>
-      <c r="F17" s="13"/>
-    </row>
-    <row r="18" spans="1:6" ht="84.4" x14ac:dyDescent="0.6">
-      <c r="B18" s="13">
+      <c r="G17" s="13"/>
+    </row>
+    <row r="18" spans="2:7" ht="85" x14ac:dyDescent="0.45">
+      <c r="C18" s="13">
         <v>46157</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="D18" s="13" t="s">
         <v>737</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="E18" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="F18" s="15" t="s">
         <v>844</v>
       </c>
-      <c r="F18" s="13"/>
-    </row>
-    <row r="20" spans="1:6" ht="34.9" x14ac:dyDescent="0.6">
-      <c r="A20" s="14" t="s">
+      <c r="G18" s="13"/>
+    </row>
+    <row r="20" spans="2:7" ht="36" x14ac:dyDescent="0.45">
+      <c r="B20" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="14"/>
-    </row>
-    <row r="21" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B21" s="134" t="s">
+      <c r="C20" s="14"/>
+    </row>
+    <row r="21" spans="2:7" ht="120" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C21" s="136" t="s">
         <v>755</v>
       </c>
-      <c r="C21" s="134"/>
-      <c r="D21" s="134"/>
-      <c r="E21" s="134"/>
-      <c r="F21" s="134"/>
-    </row>
-    <row r="23" spans="1:6" ht="34.9" x14ac:dyDescent="0.6">
-      <c r="A23" s="14" t="s">
+      <c r="D21" s="136"/>
+      <c r="E21" s="136"/>
+      <c r="F21" s="136"/>
+      <c r="G21" s="136"/>
+    </row>
+    <row r="23" spans="2:7" ht="36" x14ac:dyDescent="0.45">
+      <c r="B23" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="B23" s="14"/>
-    </row>
-    <row r="24" spans="1:6" ht="164.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="14"/>
-      <c r="B24" s="134" t="s">
+      <c r="C23" s="14"/>
+    </row>
+    <row r="24" spans="2:7" ht="164.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="14"/>
+      <c r="C24" s="136" t="s">
         <v>756</v>
       </c>
-      <c r="C24" s="134"/>
-      <c r="D24" s="134"/>
-      <c r="E24" s="134"/>
-      <c r="F24" s="134"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="C25" s="100"/>
+      <c r="D24" s="136"/>
+      <c r="E24" s="136"/>
+      <c r="F24" s="136"/>
+      <c r="G24" s="136"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
       <c r="D25" s="100"/>
       <c r="E25" s="100"/>
       <c r="F25" s="100"/>
-    </row>
-    <row r="26" spans="1:6" ht="34.9" x14ac:dyDescent="0.6">
-      <c r="A26" s="14" t="s">
+      <c r="G25" s="100"/>
+    </row>
+    <row r="26" spans="2:7" ht="36" x14ac:dyDescent="0.45">
+      <c r="B26" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="B26" s="14"/>
-    </row>
-    <row r="27" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A27" s="14"/>
-      <c r="B27" s="134" t="s">
+      <c r="C26" s="14"/>
+    </row>
+    <row r="27" spans="2:7" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="14"/>
+      <c r="C27" s="136" t="s">
         <v>738</v>
       </c>
-      <c r="C27" s="134"/>
-      <c r="D27" s="134"/>
-      <c r="E27" s="143" t="s">
+      <c r="D27" s="136"/>
+      <c r="E27" s="136"/>
+      <c r="F27" s="137" t="s">
         <v>740</v>
       </c>
-      <c r="F27" s="143"/>
-    </row>
-    <row r="28" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="14"/>
-      <c r="B28" s="134" t="s">
+      <c r="G27" s="137"/>
+    </row>
+    <row r="28" spans="2:7" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B28" s="14"/>
+      <c r="C28" s="136" t="s">
         <v>739</v>
       </c>
-      <c r="C28" s="134"/>
-      <c r="D28" s="134"/>
-      <c r="E28" s="143" t="s">
+      <c r="D28" s="136"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="137" t="s">
         <v>741</v>
       </c>
-      <c r="F28" s="143"/>
-    </row>
-    <row r="29" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="14"/>
-      <c r="B29" s="134" t="s">
+      <c r="G28" s="137"/>
+    </row>
+    <row r="29" spans="2:7" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B29" s="14"/>
+      <c r="C29" s="136" t="s">
         <v>748</v>
       </c>
-      <c r="C29" s="134"/>
-      <c r="D29" s="134"/>
-      <c r="E29" s="143" t="s">
+      <c r="D29" s="136"/>
+      <c r="E29" s="136"/>
+      <c r="F29" s="137" t="s">
         <v>742</v>
       </c>
-      <c r="F29" s="143"/>
-    </row>
-    <row r="30" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A30" s="14"/>
-      <c r="B30" s="134" t="s">
+      <c r="G29" s="137"/>
+    </row>
+    <row r="30" spans="2:7" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B30" s="14"/>
+      <c r="C30" s="136" t="s">
         <v>749</v>
       </c>
-      <c r="C30" s="134"/>
-      <c r="D30" s="134"/>
-      <c r="E30" s="143" t="s">
+      <c r="D30" s="136"/>
+      <c r="E30" s="136"/>
+      <c r="F30" s="137" t="s">
         <v>743</v>
       </c>
-      <c r="F30" s="143"/>
-    </row>
-    <row r="31" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A31" s="14"/>
-      <c r="B31" s="134" t="s">
+      <c r="G30" s="137"/>
+    </row>
+    <row r="31" spans="2:7" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="14"/>
+      <c r="C31" s="136" t="s">
         <v>750</v>
       </c>
-      <c r="C31" s="134"/>
-      <c r="D31" s="134"/>
-      <c r="E31" s="143" t="s">
+      <c r="D31" s="136"/>
+      <c r="E31" s="136"/>
+      <c r="F31" s="137" t="s">
         <v>744</v>
       </c>
-      <c r="F31" s="143"/>
-    </row>
-    <row r="32" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="14"/>
-      <c r="B32" s="134" t="s">
+      <c r="G31" s="137"/>
+    </row>
+    <row r="32" spans="2:7" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B32" s="14"/>
+      <c r="C32" s="136" t="s">
         <v>751</v>
       </c>
-      <c r="C32" s="134"/>
-      <c r="D32" s="134"/>
-      <c r="E32" s="143" t="s">
+      <c r="D32" s="136"/>
+      <c r="E32" s="136"/>
+      <c r="F32" s="137" t="s">
         <v>745</v>
       </c>
-      <c r="F32" s="143"/>
-    </row>
-    <row r="33" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="14"/>
-      <c r="B33" s="134" t="s">
+      <c r="G32" s="137"/>
+    </row>
+    <row r="33" spans="2:7" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B33" s="14"/>
+      <c r="C33" s="136" t="s">
         <v>752</v>
       </c>
-      <c r="C33" s="134"/>
-      <c r="D33" s="134"/>
-      <c r="E33" s="143" t="s">
+      <c r="D33" s="136"/>
+      <c r="E33" s="136"/>
+      <c r="F33" s="137" t="s">
         <v>746</v>
       </c>
-      <c r="F33" s="143"/>
-    </row>
-    <row r="34" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="14"/>
-      <c r="B34" s="134" t="s">
+      <c r="G33" s="137"/>
+    </row>
+    <row r="34" spans="2:7" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B34" s="14"/>
+      <c r="C34" s="136" t="s">
         <v>753</v>
       </c>
-      <c r="C34" s="134"/>
-      <c r="D34" s="134"/>
-      <c r="E34" s="143" t="s">
+      <c r="D34" s="136"/>
+      <c r="E34" s="136"/>
+      <c r="F34" s="137" t="s">
         <v>747</v>
       </c>
-      <c r="F34" s="143"/>
-    </row>
-    <row r="36" spans="1:6" ht="34.9" x14ac:dyDescent="0.6">
-      <c r="A36" s="14" t="s">
+      <c r="G34" s="137"/>
+    </row>
+    <row r="36" spans="2:7" ht="36" x14ac:dyDescent="0.45">
+      <c r="B36" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="B36" s="14"/>
-    </row>
-    <row r="37" spans="1:6" ht="95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B37" s="131" t="s">
+      <c r="C36" s="14"/>
+    </row>
+    <row r="37" spans="2:7" ht="95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C37" s="138" t="s">
         <v>754</v>
       </c>
-      <c r="C37" s="132"/>
-      <c r="D37" s="132"/>
-      <c r="E37" s="132"/>
-      <c r="F37" s="133"/>
+      <c r="D37" s="139"/>
+      <c r="E37" s="139"/>
+      <c r="F37" s="139"/>
+      <c r="G37" s="140"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:G33"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E27:F27" location="스테이터스!A1" display="‘스테이터스’ 시트" xr:uid="{1F54D77E-790C-4B5C-AB45-02ABD2DAF460}"/>
-    <hyperlink ref="E28:F28" location="'성장 시스템'!A1" display="‘성장 시스템’ 시트" xr:uid="{FB89F930-A8EF-416B-935E-16E783B012B4}"/>
-    <hyperlink ref="E29:F29" location="'아군 유닛'!A1" display="‘아군 유닛’ 시트" xr:uid="{37E20B0B-30E4-4FC2-9C3C-064499223373}"/>
-    <hyperlink ref="E30:F30" location="'적군 유닛'!A1" display="‘적군 유닛’ 시트" xr:uid="{CD8A4F41-0D06-4AB5-B107-292FCDCE2670}"/>
-    <hyperlink ref="E31:F31" location="'직업 스킬'!A1" display="‘직업 스킬’ 시트" xr:uid="{AF396A14-A42D-4585-AAD6-09D133571A08}"/>
-    <hyperlink ref="E32:F32" location="무기!A1" display="‘무기’ 시트" xr:uid="{63AF4BFB-7E39-4DF4-A9B2-D04952C7F2DE}"/>
-    <hyperlink ref="E33:F33" location="'스탯 시뮬레이터'!A1" display="‘스탯 시뮬레이터’ 시트" xr:uid="{20170922-DB62-4CCE-8C9F-CC3826D67881}"/>
-    <hyperlink ref="E34:F34" location="'전투 시뮬레이터'!A1" display="‘전투 시뮬레이터’ 시트" xr:uid="{75F07108-D2AE-4083-B151-1F77BC98A062}"/>
+    <hyperlink ref="F27:G27" location="스테이터스!A1" display="‘스테이터스’ 시트" xr:uid="{1F54D77E-790C-4B5C-AB45-02ABD2DAF460}"/>
+    <hyperlink ref="F28:G28" location="'성장 시스템'!A1" display="‘성장 시스템’ 시트" xr:uid="{FB89F930-A8EF-416B-935E-16E783B012B4}"/>
+    <hyperlink ref="F29:G29" location="'아군 유닛'!A1" display="‘아군 유닛’ 시트" xr:uid="{37E20B0B-30E4-4FC2-9C3C-064499223373}"/>
+    <hyperlink ref="F30:G30" location="'적군 유닛'!A1" display="‘적군 유닛’ 시트" xr:uid="{CD8A4F41-0D06-4AB5-B107-292FCDCE2670}"/>
+    <hyperlink ref="F31:G31" location="'직업 스킬'!A1" display="‘직업 스킬’ 시트" xr:uid="{AF396A14-A42D-4585-AAD6-09D133571A08}"/>
+    <hyperlink ref="F32:G32" location="무기!A1" display="‘무기’ 시트" xr:uid="{63AF4BFB-7E39-4DF4-A9B2-D04952C7F2DE}"/>
+    <hyperlink ref="F33:G33" location="'스탯 시뮬레이터'!A1" display="‘스탯 시뮬레이터’ 시트" xr:uid="{20170922-DB62-4CCE-8C9F-CC3826D67881}"/>
+    <hyperlink ref="F34:G34" location="'전투 시뮬레이터'!A1" display="‘전투 시뮬레이터’ 시트" xr:uid="{75F07108-D2AE-4083-B151-1F77BC98A062}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5441,22 +5485,22 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3BC3889-A9A5-4973-A040-073F596EADE3}">
   <dimension ref="A1:AL17"/>
-  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="3" width="20.5625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="30.5625" style="8" customWidth="1"/>
-    <col min="5" max="16" width="20.5625" style="8" customWidth="1"/>
-    <col min="17" max="17" width="20.5625" style="39" customWidth="1"/>
-    <col min="18" max="18" width="20.5625" style="35" customWidth="1"/>
-    <col min="19" max="19" width="20.5625" style="8" customWidth="1"/>
-    <col min="20" max="20" width="65.5625" style="18" customWidth="1"/>
-    <col min="21" max="21" width="20.5625" style="18" customWidth="1"/>
-    <col min="22" max="28" width="20.5625" style="8" customWidth="1"/>
-    <col min="29" max="34" width="25.5625" style="8" customWidth="1"/>
-    <col min="35" max="16384" width="8.5625" style="1"/>
+    <col min="1" max="3" width="20.58203125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="30.58203125" style="8" customWidth="1"/>
+    <col min="5" max="16" width="20.58203125" style="8" customWidth="1"/>
+    <col min="17" max="17" width="20.58203125" style="39" customWidth="1"/>
+    <col min="18" max="18" width="20.58203125" style="35" customWidth="1"/>
+    <col min="19" max="19" width="20.58203125" style="8" customWidth="1"/>
+    <col min="20" max="20" width="65.58203125" style="18" customWidth="1"/>
+    <col min="21" max="21" width="20.58203125" style="18" customWidth="1"/>
+    <col min="22" max="28" width="20.58203125" style="8" customWidth="1"/>
+    <col min="29" max="34" width="25.58203125" style="8" customWidth="1"/>
+    <col min="35" max="16384" width="8.58203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:38" ht="34" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>109</v>
       </c>
@@ -5560,7 +5604,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="2" spans="1:38" ht="101.25" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:38" ht="102" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>89</v>
       </c>
@@ -5663,13 +5707,13 @@
       <c r="AH2" s="129" t="s">
         <v>777</v>
       </c>
-      <c r="AJ2" s="138" t="s">
+      <c r="AJ2" s="144" t="s">
         <v>295</v>
       </c>
-      <c r="AK2" s="138"/>
-      <c r="AL2" s="138"/>
-    </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.6">
+      <c r="AK2" s="144"/>
+      <c r="AL2" s="144"/>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A3" s="8">
         <v>310101</v>
       </c>
@@ -5745,7 +5789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A4" s="8">
         <v>310102</v>
       </c>
@@ -5825,7 +5869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A5" s="8">
         <v>310103</v>
       </c>
@@ -5904,7 +5948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A6" s="10">
         <v>310201</v>
       </c>
@@ -5963,23 +6007,23 @@
       <c r="Z6" s="10"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="10"/>
-      <c r="AC6" s="144">
+      <c r="AC6" s="132">
         <v>1.5</v>
       </c>
-      <c r="AD6" s="144"/>
-      <c r="AE6" s="144">
+      <c r="AD6" s="132"/>
+      <c r="AE6" s="132">
         <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
-      <c r="AF6" s="144" t="str">
+      <c r="AF6" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AG6" s="144">
+      <c r="AG6" s="132">
         <f t="shared" si="3"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="AH6" s="144" t="str">
+      <c r="AH6" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -5990,7 +6034,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:38" ht="34" x14ac:dyDescent="0.45">
       <c r="A7" s="10">
         <v>310202</v>
       </c>
@@ -6059,30 +6103,30 @@
       <c r="AB7" s="10">
         <v>1</v>
       </c>
-      <c r="AC7" s="144">
+      <c r="AC7" s="132">
         <v>0.8</v>
       </c>
-      <c r="AD7" s="144">
+      <c r="AD7" s="132">
         <v>0.8</v>
       </c>
-      <c r="AE7" s="144">
+      <c r="AE7" s="132">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AF7" s="144">
+      <c r="AF7" s="132">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AG7" s="144">
+      <c r="AG7" s="132">
         <f t="shared" si="3"/>
         <v>1.2</v>
       </c>
-      <c r="AH7" s="144">
+      <c r="AH7" s="132">
         <f t="shared" si="4"/>
         <v>1.2</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A8" s="10">
         <v>310203</v>
       </c>
@@ -6145,28 +6189,28 @@
       <c r="Z8" s="10"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="10"/>
-      <c r="AC8" s="144">
+      <c r="AC8" s="132">
         <v>1.2</v>
       </c>
-      <c r="AD8" s="144"/>
-      <c r="AE8" s="144">
+      <c r="AD8" s="132"/>
+      <c r="AE8" s="132">
         <f t="shared" si="1"/>
         <v>1.4</v>
       </c>
-      <c r="AF8" s="144" t="str">
+      <c r="AF8" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AG8" s="144">
+      <c r="AG8" s="132">
         <f t="shared" si="3"/>
         <v>1.7</v>
       </c>
-      <c r="AH8" s="144" t="str">
+      <c r="AH8" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A9" s="8">
         <v>310301</v>
       </c>
@@ -6215,10 +6259,10 @@
       <c r="Z9" s="18"/>
       <c r="AA9" s="18"/>
       <c r="AB9" s="18"/>
-      <c r="AC9" s="145">
+      <c r="AC9" s="133">
         <v>1.5</v>
       </c>
-      <c r="AD9" s="145"/>
+      <c r="AD9" s="133"/>
       <c r="AE9" s="33">
         <f t="shared" si="1"/>
         <v>1.8</v>
@@ -6236,7 +6280,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:38" ht="34" x14ac:dyDescent="0.45">
       <c r="A10" s="8">
         <v>310302</v>
       </c>
@@ -6293,10 +6337,10 @@
         <v>0</v>
       </c>
       <c r="AB10" s="18"/>
-      <c r="AC10" s="145">
+      <c r="AC10" s="133">
         <v>1.2</v>
       </c>
-      <c r="AD10" s="145"/>
+      <c r="AD10" s="133"/>
       <c r="AE10" s="33">
         <f t="shared" si="1"/>
         <v>1.4</v>
@@ -6314,7 +6358,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:38" ht="34" x14ac:dyDescent="0.45">
       <c r="A11" s="8">
         <v>310303</v>
       </c>
@@ -6366,10 +6410,10 @@
       <c r="Z11" s="18"/>
       <c r="AA11" s="18"/>
       <c r="AB11" s="18"/>
-      <c r="AC11" s="145">
+      <c r="AC11" s="133">
         <v>1.2</v>
       </c>
-      <c r="AD11" s="145">
+      <c r="AD11" s="133">
         <v>1.2</v>
       </c>
       <c r="AE11" s="33">
@@ -6389,7 +6433,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A12" s="10">
         <v>310401</v>
       </c>
@@ -6448,28 +6492,28 @@
       <c r="Z12" s="45"/>
       <c r="AA12" s="45"/>
       <c r="AB12" s="45"/>
-      <c r="AC12" s="146">
+      <c r="AC12" s="134">
         <v>1.5</v>
       </c>
-      <c r="AD12" s="146"/>
-      <c r="AE12" s="144">
+      <c r="AD12" s="134"/>
+      <c r="AE12" s="132">
         <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
-      <c r="AF12" s="144" t="str">
+      <c r="AF12" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AG12" s="144">
+      <c r="AG12" s="132">
         <f t="shared" si="3"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="AH12" s="144" t="str">
+      <c r="AH12" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:38" ht="34" x14ac:dyDescent="0.45">
       <c r="A13" s="10">
         <v>310402</v>
       </c>
@@ -6530,28 +6574,28 @@
       <c r="Z13" s="45"/>
       <c r="AA13" s="45"/>
       <c r="AB13" s="45"/>
-      <c r="AC13" s="146">
+      <c r="AC13" s="134">
         <v>1.8</v>
       </c>
-      <c r="AD13" s="146"/>
-      <c r="AE13" s="144">
+      <c r="AD13" s="134"/>
+      <c r="AE13" s="132">
         <f t="shared" si="1"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="AF13" s="144" t="str">
+      <c r="AF13" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AG13" s="144">
+      <c r="AG13" s="132">
         <f t="shared" si="3"/>
         <v>2.6</v>
       </c>
-      <c r="AH13" s="144" t="str">
+      <c r="AH13" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:38" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:38" ht="34" x14ac:dyDescent="0.45">
       <c r="A14" s="10">
         <v>310403</v>
       </c>
@@ -6612,28 +6656,28 @@
       <c r="Z14" s="45"/>
       <c r="AA14" s="45"/>
       <c r="AB14" s="45"/>
-      <c r="AC14" s="146">
+      <c r="AC14" s="134">
         <v>1.5</v>
       </c>
-      <c r="AD14" s="146"/>
-      <c r="AE14" s="144">
+      <c r="AD14" s="134"/>
+      <c r="AE14" s="132">
         <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
-      <c r="AF14" s="144" t="str">
+      <c r="AF14" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AG14" s="144">
+      <c r="AG14" s="132">
         <f t="shared" si="3"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="AH14" s="144" t="str">
+      <c r="AH14" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A15" s="8">
         <v>310501</v>
       </c>
@@ -6700,7 +6744,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:38" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:38" ht="34" x14ac:dyDescent="0.45">
       <c r="A16" s="8">
         <v>310502</v>
       </c>
@@ -6773,7 +6817,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.45">
       <c r="A17" s="8">
         <v>310503</v>
       </c>
@@ -6856,17 +6900,17 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ACAB2BB-5153-4042-B043-B1CF0992DABC}">
   <dimension ref="A1:N41"/>
-  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.0625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.08203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.9375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16" width="25.5625" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.5625" style="1"/>
+    <col min="4" max="4" width="32.9140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16" width="25.58203125" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.58203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
         <v>339</v>
       </c>
@@ -6874,27 +6918,27 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B2" s="65" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:14" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B3" s="66" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B4" s="68" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="35.25" thickTop="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:14" ht="36.5" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A5" s="14" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:14" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B6" s="4" t="s">
         <v>255</v>
       </c>
@@ -6935,7 +6979,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="7" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B7" s="5">
         <v>1</v>
       </c>
@@ -6944,7 +6988,7 @@
         <v>가디언</v>
       </c>
       <c r="D7" s="64" t="str">
-        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$C$2:$G$7,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$D$3:$H$8,2,FALSE),"")</f>
         <v>체력이 높은 근거리 병종</v>
       </c>
       <c r="E7" s="52">
@@ -6959,35 +7003,35 @@
         <v>100</v>
       </c>
       <c r="H7" s="51">
-        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$C$2:$K$7,COLUMN(A1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$D$3:$L$8,COLUMN(A1)+2,FALSE),"")</f>
         <v>7</v>
       </c>
       <c r="I7" s="51">
-        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$C$2:$K$7,COLUMN(B1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$D$3:$L$8,COLUMN(B1)+2,FALSE),"")</f>
         <v>7</v>
       </c>
       <c r="J7" s="51">
-        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$C$2:$K$7,COLUMN(C1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$D$3:$L$8,COLUMN(C1)+2,FALSE),"")</f>
         <v>6</v>
       </c>
       <c r="K7" s="72">
-        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$C$2:$K$7,COLUMN(D1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$D$3:$L$8,COLUMN(D1)+2,FALSE),"")</f>
         <v>0.1</v>
       </c>
       <c r="L7" s="72">
-        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$C$2:$K$7,COLUMN(E1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$D$3:$L$8,COLUMN(E1)+2,FALSE),"")</f>
         <v>0.25</v>
       </c>
       <c r="M7" s="72">
-        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$C$2:$K$7,COLUMN(F1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$D$3:$L$8,COLUMN(F1)+2,FALSE),"")</f>
         <v>0.1</v>
       </c>
       <c r="N7" s="51">
-        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$C$2:$K$7,COLUMN(G1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C7,'아군 유닛'!$D$3:$L$8,COLUMN(G1)+2,FALSE),"")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="8" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" s="5">
         <v>2</v>
       </c>
@@ -6995,7 +7039,7 @@
         <v>549</v>
       </c>
       <c r="D8" s="64" t="str">
-        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$C$2:$G$7,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$D$3:$H$8,2,FALSE),"")</f>
         <v>체력이 높은 근거리 병종</v>
       </c>
       <c r="E8" s="52">
@@ -7010,35 +7054,35 @@
         <v>100</v>
       </c>
       <c r="H8" s="51">
-        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$C$2:$K$7,COLUMN(A1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$D$3:$L$8,COLUMN(A1)+2,FALSE),"")</f>
         <v>7</v>
       </c>
       <c r="I8" s="51">
-        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$C$2:$K$7,COLUMN(B1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$D$3:$L$8,COLUMN(B1)+2,FALSE),"")</f>
         <v>7</v>
       </c>
       <c r="J8" s="51">
-        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$C$2:$K$7,COLUMN(C1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$D$3:$L$8,COLUMN(C1)+2,FALSE),"")</f>
         <v>6</v>
       </c>
       <c r="K8" s="72">
-        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$C$2:$K$7,COLUMN(D1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$D$3:$L$8,COLUMN(D1)+2,FALSE),"")</f>
         <v>0.1</v>
       </c>
       <c r="L8" s="72">
-        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$C$2:$K$7,COLUMN(E1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$D$3:$L$8,COLUMN(E1)+2,FALSE),"")</f>
         <v>0.25</v>
       </c>
       <c r="M8" s="72">
-        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$C$2:$K$7,COLUMN(F1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$D$3:$L$8,COLUMN(F1)+2,FALSE),"")</f>
         <v>0.1</v>
       </c>
       <c r="N8" s="51">
-        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$C$2:$K$7,COLUMN(G1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C8,'아군 유닛'!$D$3:$L$8,COLUMN(G1)+2,FALSE),"")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="9" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="5">
         <v>3</v>
       </c>
@@ -7046,7 +7090,7 @@
         <v>554</v>
       </c>
       <c r="D9" s="64" t="str">
-        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$C$2:$G$7,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$D$3:$H$8,2,FALSE),"")</f>
         <v>평균적인 능력치를 지닌 근거리 병종</v>
       </c>
       <c r="E9" s="52">
@@ -7061,35 +7105,35 @@
         <v>100</v>
       </c>
       <c r="H9" s="51">
-        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$C$2:$K$7,COLUMN(A1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$D$3:$L$8,COLUMN(A1)+2,FALSE),"")</f>
         <v>6</v>
       </c>
       <c r="I9" s="51">
-        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$C$2:$K$7,COLUMN(B1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$D$3:$L$8,COLUMN(B1)+2,FALSE),"")</f>
         <v>9</v>
       </c>
       <c r="J9" s="51">
-        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$C$2:$K$7,COLUMN(C1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$D$3:$L$8,COLUMN(C1)+2,FALSE),"")</f>
         <v>5</v>
       </c>
       <c r="K9" s="72">
-        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$C$2:$K$7,COLUMN(D1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$D$3:$L$8,COLUMN(D1)+2,FALSE),"")</f>
         <v>0.15</v>
       </c>
       <c r="L9" s="72">
-        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$C$2:$K$7,COLUMN(E1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$D$3:$L$8,COLUMN(E1)+2,FALSE),"")</f>
         <v>0.15</v>
       </c>
       <c r="M9" s="72">
-        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$C$2:$K$7,COLUMN(F1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$D$3:$L$8,COLUMN(F1)+2,FALSE),"")</f>
         <v>0.15</v>
       </c>
       <c r="N9" s="51">
-        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$C$2:$K$7,COLUMN(G1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C9,'아군 유닛'!$D$3:$L$8,COLUMN(G1)+2,FALSE),"")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="10" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="5">
         <v>4</v>
       </c>
@@ -7097,7 +7141,7 @@
         <v>552</v>
       </c>
       <c r="D10" s="64" t="str">
-        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$C$2:$G$7,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$D$3:$H$8,2,FALSE),"")</f>
         <v>회복이 가능한 원거리 병종</v>
       </c>
       <c r="E10" s="52">
@@ -7112,41 +7156,41 @@
         <v>100</v>
       </c>
       <c r="H10" s="51">
-        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$C$2:$K$7,COLUMN(A1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$D$3:$L$8,COLUMN(A1)+2,FALSE),"")</f>
         <v>6</v>
       </c>
       <c r="I10" s="51">
-        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$C$2:$K$7,COLUMN(B1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$D$3:$L$8,COLUMN(B1)+2,FALSE),"")</f>
         <v>8</v>
       </c>
       <c r="J10" s="51">
-        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$C$2:$K$7,COLUMN(C1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$D$3:$L$8,COLUMN(C1)+2,FALSE),"")</f>
         <v>6</v>
       </c>
       <c r="K10" s="72">
-        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$C$2:$K$7,COLUMN(D1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$D$3:$L$8,COLUMN(D1)+2,FALSE),"")</f>
         <v>0.1</v>
       </c>
       <c r="L10" s="72">
-        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$C$2:$K$7,COLUMN(E1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$D$3:$L$8,COLUMN(E1)+2,FALSE),"")</f>
         <v>0.1</v>
       </c>
       <c r="M10" s="72">
-        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$C$2:$K$7,COLUMN(F1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$D$3:$L$8,COLUMN(F1)+2,FALSE),"")</f>
         <v>0.15</v>
       </c>
       <c r="N10" s="51">
-        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$C$2:$K$7,COLUMN(G1)+2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($C10,'아군 유닛'!$D$3:$L$8,COLUMN(G1)+2,FALSE),"")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="17.25" thickTop="1" x14ac:dyDescent="0.6"/>
-    <row r="12" spans="1:14" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:14" ht="17.5" thickTop="1" x14ac:dyDescent="0.45"/>
+    <row r="12" spans="1:14" ht="36" x14ac:dyDescent="0.45">
       <c r="A12" s="14" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="84.75" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="13" spans="1:14" ht="85.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B13" s="4" t="s">
         <v>255</v>
       </c>
@@ -7175,7 +7219,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="14" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B14" s="5">
         <v>1</v>
       </c>
@@ -7212,7 +7256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="15" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B15" s="5">
         <v>2</v>
       </c>
@@ -7248,7 +7292,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="16" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B16" s="5">
         <v>3</v>
       </c>
@@ -7284,7 +7328,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="17" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B17" s="5">
         <v>4</v>
       </c>
@@ -7320,25 +7364,25 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.6"/>
-    <row r="19" spans="1:10" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:10" ht="17.5" thickTop="1" x14ac:dyDescent="0.45"/>
+    <row r="19" spans="1:10" ht="36" x14ac:dyDescent="0.45">
       <c r="A19" s="14" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:10" ht="36" x14ac:dyDescent="0.45">
       <c r="B20" s="14"/>
-      <c r="D20" s="139" t="s">
+      <c r="D20" s="145" t="s">
         <v>272</v>
       </c>
-      <c r="E20" s="140"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="140"/>
-      <c r="J20" s="141"/>
-    </row>
-    <row r="21" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="E20" s="146"/>
+      <c r="F20" s="146"/>
+      <c r="G20" s="146"/>
+      <c r="H20" s="146"/>
+      <c r="I20" s="146"/>
+      <c r="J20" s="147"/>
+    </row>
+    <row r="21" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="4" t="s">
         <v>255</v>
       </c>
@@ -7367,7 +7411,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B22" s="5">
         <v>1</v>
       </c>
@@ -7403,7 +7447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B23" s="5">
         <v>2</v>
       </c>
@@ -7439,7 +7483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B24" s="5">
         <v>3</v>
       </c>
@@ -7475,7 +7519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B25" s="5">
         <v>4</v>
       </c>
@@ -7511,12 +7555,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:10" ht="36" x14ac:dyDescent="0.45">
       <c r="A27" s="14" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="28" spans="1:10" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B28" s="4" t="s">
         <v>255</v>
       </c>
@@ -7542,7 +7586,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="85.15" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="29" spans="1:10" ht="86" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B29" s="5">
         <v>1</v>
       </c>
@@ -7574,7 +7618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="34.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="30" spans="1:10" ht="35" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B30" s="5">
         <v>2</v>
       </c>
@@ -7606,7 +7650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="34.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="31" spans="1:10" ht="35" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B31" s="5">
         <v>3</v>
       </c>
@@ -7638,7 +7682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="34.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="32" spans="1:10" ht="35" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B32" s="5">
         <v>4</v>
       </c>
@@ -7670,24 +7714,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="17.25" thickTop="1" x14ac:dyDescent="0.6"/>
-    <row r="34" spans="1:14" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:14" ht="17.5" thickTop="1" x14ac:dyDescent="0.45"/>
+    <row r="34" spans="1:14" ht="36" x14ac:dyDescent="0.45">
       <c r="A34" s="14" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="E35" s="139" t="s">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="E35" s="145" t="s">
         <v>344</v>
       </c>
-      <c r="F35" s="140"/>
-      <c r="G35" s="140"/>
-      <c r="H35" s="140"/>
-      <c r="I35" s="140"/>
-      <c r="J35" s="140"/>
-      <c r="K35" s="141"/>
-    </row>
-    <row r="36" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="F35" s="146"/>
+      <c r="G35" s="146"/>
+      <c r="H35" s="146"/>
+      <c r="I35" s="146"/>
+      <c r="J35" s="146"/>
+      <c r="K35" s="147"/>
+    </row>
+    <row r="36" spans="1:14" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B36" s="4" t="s">
         <v>255</v>
       </c>
@@ -7728,7 +7772,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="37" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B37" s="5">
         <v>1</v>
       </c>
@@ -7781,7 +7825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="38" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B38" s="5">
         <v>2</v>
       </c>
@@ -7834,7 +7878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="39" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B39" s="5">
         <v>3</v>
       </c>
@@ -7887,7 +7931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="40" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B40" s="5">
         <v>4</v>
       </c>
@@ -7940,7 +7984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="17.25" thickTop="1" x14ac:dyDescent="0.6"/>
+    <row r="41" spans="1:14" ht="17.5" thickTop="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D20:J20"/>
@@ -8009,7 +8053,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6FDBFB6A-D685-486E-8623-A7EBE6F25DCE}">
           <x14:formula1>
-            <xm:f>'아군 유닛'!$C$3:$C$7</xm:f>
+            <xm:f>'아군 유닛'!$D$4:$D$8</xm:f>
           </x14:formula1>
           <xm:sqref>C8:C10</xm:sqref>
         </x14:dataValidation>
@@ -8022,36 +8066,36 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08896B46-0194-4E63-B8F8-7513BFA97295}">
   <dimension ref="A2:O31"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.6875" style="16"/>
-    <col min="2" max="2" width="20.5625" style="16" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="16"/>
+    <col min="2" max="2" width="20.58203125" style="16" customWidth="1"/>
     <col min="3" max="3" width="22.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="20.5625" style="16" customWidth="1"/>
+    <col min="4" max="12" width="20.58203125" style="16" customWidth="1"/>
     <col min="13" max="13" width="13.75" style="16" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.75" style="16" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18" style="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.6875" style="16"/>
+    <col min="16" max="16384" width="8.6640625" style="16"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:15" ht="36" x14ac:dyDescent="0.45">
       <c r="A2" s="86" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="125.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B3" s="134" t="s">
+    <row r="3" spans="1:15" ht="125.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="136" t="s">
         <v>603</v>
       </c>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
-      <c r="I3" s="134"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.6">
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C4" s="100"/>
       <c r="D4" s="100"/>
       <c r="E4" s="100"/>
@@ -8060,44 +8104,44 @@
       <c r="H4" s="100"/>
       <c r="I4" s="100"/>
     </row>
-    <row r="5" spans="1:15" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:15" ht="36" x14ac:dyDescent="0.45">
       <c r="A5" s="86" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="252" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B6" s="134" t="s">
+    <row r="6" spans="1:15" ht="252" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="136" t="s">
         <v>481</v>
       </c>
-      <c r="C6" s="134"/>
-      <c r="D6" s="134"/>
-      <c r="E6" s="134"/>
-      <c r="F6" s="134"/>
-      <c r="G6" s="134"/>
-      <c r="H6" s="134"/>
-      <c r="I6" s="134"/>
-    </row>
-    <row r="8" spans="1:15" ht="34.9" x14ac:dyDescent="0.6">
+      <c r="C6" s="136"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+    </row>
+    <row r="8" spans="1:15" ht="36" x14ac:dyDescent="0.45">
       <c r="A8" s="86" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.6">
-      <c r="B9" s="142" t="s">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="B9" s="148" t="s">
         <v>339</v>
       </c>
       <c r="C9" s="82" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.6">
-      <c r="B10" s="142"/>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="B10" s="148"/>
       <c r="C10" s="83" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B11" s="142"/>
+    <row r="11" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B11" s="148"/>
       <c r="C11" s="84" t="s">
         <v>341</v>
       </c>
@@ -8105,25 +8149,25 @@
         <v>379</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
-      <c r="B12" s="142"/>
+    <row r="12" spans="1:15" ht="17.5" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="148"/>
       <c r="C12" s="85" t="s">
         <v>343</v>
       </c>
-      <c r="G12" s="139" t="s">
+      <c r="G12" s="145" t="s">
         <v>352</v>
       </c>
-      <c r="H12" s="140"/>
-      <c r="I12" s="140"/>
-      <c r="J12" s="140"/>
-      <c r="K12" s="140"/>
-      <c r="L12" s="140"/>
-      <c r="M12" s="141"/>
+      <c r="H12" s="146"/>
+      <c r="I12" s="146"/>
+      <c r="J12" s="146"/>
+      <c r="K12" s="146"/>
+      <c r="L12" s="146"/>
+      <c r="M12" s="147"/>
       <c r="O12" s="63">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:15" ht="34" x14ac:dyDescent="0.45">
       <c r="B13" s="79"/>
       <c r="C13" s="79" t="s">
         <v>475</v>
@@ -8165,7 +8209,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B14" s="79" t="s">
         <v>351</v>
       </c>
@@ -8218,7 +8262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B15" s="79" t="s">
         <v>378</v>
       </c>
@@ -8264,7 +8308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:4" ht="34" x14ac:dyDescent="0.45">
       <c r="B19" s="79" t="s">
         <v>360</v>
       </c>
@@ -8275,7 +8319,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B20" s="79">
         <v>0</v>
       </c>
@@ -8288,7 +8332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B21" s="79">
         <v>1</v>
       </c>
@@ -8301,7 +8345,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B22" s="79">
         <v>2</v>
       </c>
@@ -8314,7 +8358,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B23" s="79">
         <v>3</v>
       </c>
@@ -8327,7 +8371,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B24" s="79">
         <v>4</v>
       </c>
@@ -8340,7 +8384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B25" s="79">
         <v>5</v>
       </c>
@@ -8353,7 +8397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B26" s="79">
         <v>6</v>
       </c>
@@ -8366,7 +8410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B27" s="79">
         <v>7</v>
       </c>
@@ -8379,7 +8423,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B28" s="79">
         <v>8</v>
       </c>
@@ -8392,7 +8436,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B29" s="79">
         <v>9</v>
       </c>
@@ -8405,7 +8449,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B30" s="79">
         <v>10</v>
       </c>
@@ -8418,7 +8462,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B31" s="67" t="s">
         <v>363</v>
       </c>
@@ -8467,7 +8511,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D2F0DF62-9D9B-454C-93A3-1E7382067C64}">
           <x14:formula1>
-            <xm:f>'아군 유닛'!$C$3:$C$7</xm:f>
+            <xm:f>'아군 유닛'!$D$4:$D$8</xm:f>
           </x14:formula1>
           <xm:sqref>C14</xm:sqref>
         </x14:dataValidation>
@@ -8486,21 +8530,21 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D4E019-5C34-4D8E-8908-3BB36F3EC416}">
   <dimension ref="A1:O83"/>
-  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.0625" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.0625" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="9" width="14.8125" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="8.5625" style="16"/>
-    <col min="12" max="12" width="11.0625" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="14.8125" style="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="8.5625" style="16"/>
-    <col min="21" max="21" width="7.3125" style="16" customWidth="1"/>
-    <col min="22" max="22" width="29.8125" style="16" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.5625" style="16"/>
+    <col min="1" max="1" width="11.08203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="14.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="8.58203125" style="16"/>
+    <col min="12" max="12" width="11.08203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="8.58203125" style="16"/>
+    <col min="21" max="21" width="7.33203125" style="16" customWidth="1"/>
+    <col min="22" max="22" width="29.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.58203125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>259</v>
       </c>
@@ -8541,7 +8585,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" s="8" t="str">
         <f>'스탯 시뮬레이터'!C7</f>
         <v>가디언</v>
@@ -8599,7 +8643,7 @@
         <v>상급 수호의 코어</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="str">
         <f>'스탯 시뮬레이터'!C8</f>
         <v>가디언</v>
@@ -8657,7 +8701,7 @@
         <v>상급 수호의 코어</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="str">
         <f>'스탯 시뮬레이터'!C9</f>
         <v>파이터</v>
@@ -8715,7 +8759,7 @@
         <v>상급 투쟁의 코어</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="str">
         <f>'스탯 시뮬레이터'!C10</f>
         <v>서포터</v>
@@ -8773,7 +8817,7 @@
         <v>상급 회복의 코어</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" s="5" t="s">
         <v>116</v>
       </c>
@@ -8814,7 +8858,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" s="48" t="s">
         <v>549</v>
       </c>
@@ -8843,7 +8887,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" s="8" t="s">
         <v>549</v>
       </c>
@@ -8872,7 +8916,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" s="48" t="s">
         <v>549</v>
       </c>
@@ -8903,7 +8947,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" s="8" t="s">
         <v>549</v>
       </c>
@@ -8934,7 +8978,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" s="48" t="s">
         <v>549</v>
       </c>
@@ -8967,7 +9011,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" s="8" t="s">
         <v>549</v>
       </c>
@@ -8988,7 +9032,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" s="48" t="s">
         <v>549</v>
       </c>
@@ -9017,7 +9061,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" s="8" t="s">
         <v>549</v>
       </c>
@@ -9046,7 +9090,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" s="8" t="s">
         <v>549</v>
       </c>
@@ -9075,7 +9119,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" s="48" t="s">
         <v>549</v>
       </c>
@@ -9106,7 +9150,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A18" s="8" t="s">
         <v>549</v>
       </c>
@@ -9137,7 +9181,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A19" s="48" t="s">
         <v>549</v>
       </c>
@@ -9170,7 +9214,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A20" s="8" t="s">
         <v>549</v>
       </c>
@@ -9203,7 +9247,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A21" s="8" t="s">
         <v>549</v>
       </c>
@@ -9236,7 +9280,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="22" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22" s="48" t="s">
         <v>549</v>
       </c>
@@ -9271,7 +9315,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="23" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="52" t="s">
         <v>551</v>
       </c>
@@ -9294,7 +9338,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="24" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A24" s="10" t="s">
         <v>551</v>
       </c>
@@ -9317,7 +9361,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="25" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A25" s="52" t="s">
         <v>551</v>
       </c>
@@ -9342,7 +9386,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="26" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A26" s="10" t="s">
         <v>551</v>
       </c>
@@ -9367,7 +9411,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="27" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A27" s="52" t="s">
         <v>551</v>
       </c>
@@ -9394,7 +9438,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="28" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A28" s="10" t="s">
         <v>551</v>
       </c>
@@ -9421,7 +9465,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="29" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A29" s="52" t="s">
         <v>551</v>
       </c>
@@ -9450,7 +9494,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:13" ht="17.5" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A30" s="10" t="s">
         <v>551</v>
       </c>
@@ -9473,7 +9517,7 @@
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
     </row>
-    <row r="31" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="31" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A31" s="10" t="s">
         <v>551</v>
       </c>
@@ -9496,7 +9540,7 @@
       <c r="H31" s="10"/>
       <c r="I31" s="10"/>
     </row>
-    <row r="32" spans="1:13" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="32" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A32" s="52" t="s">
         <v>551</v>
       </c>
@@ -9521,7 +9565,7 @@
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
     </row>
-    <row r="33" spans="1:9" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="33" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A33" s="10" t="s">
         <v>551</v>
       </c>
@@ -9546,7 +9590,7 @@
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="1:9" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="34" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A34" s="52" t="s">
         <v>551</v>
       </c>
@@ -9573,7 +9617,7 @@
       </c>
       <c r="I34" s="10"/>
     </row>
-    <row r="35" spans="1:9" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:9" ht="17.5" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A35" s="10" t="s">
         <v>551</v>
       </c>
@@ -9600,7 +9644,7 @@
       </c>
       <c r="I35" s="10"/>
     </row>
-    <row r="36" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="36" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A36" s="10" t="s">
         <v>551</v>
       </c>
@@ -9627,7 +9671,7 @@
       </c>
       <c r="I36" s="10"/>
     </row>
-    <row r="37" spans="1:9" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="37" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A37" s="52" t="s">
         <v>551</v>
       </c>
@@ -9656,7 +9700,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:9" ht="17.5" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A38" s="48" t="s">
         <v>550</v>
       </c>
@@ -9673,7 +9717,7 @@
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" s="8" t="s">
         <v>550</v>
       </c>
@@ -9690,7 +9734,7 @@
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" s="48" t="s">
         <v>550</v>
       </c>
@@ -9709,7 +9753,7 @@
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41" s="8" t="s">
         <v>550</v>
       </c>
@@ -9728,7 +9772,7 @@
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" s="48" t="s">
         <v>550</v>
       </c>
@@ -9749,7 +9793,7 @@
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" s="8" t="s">
         <v>550</v>
       </c>
@@ -9770,7 +9814,7 @@
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" s="48" t="s">
         <v>550</v>
       </c>
@@ -9793,7 +9837,7 @@
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45" s="8" t="s">
         <v>550</v>
       </c>
@@ -9816,7 +9860,7 @@
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46" s="8" t="s">
         <v>550</v>
       </c>
@@ -9839,7 +9883,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47" s="48" t="s">
         <v>550</v>
       </c>
@@ -9864,7 +9908,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48" s="8" t="s">
         <v>550</v>
       </c>
@@ -9889,7 +9933,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49" s="48" t="s">
         <v>550</v>
       </c>
@@ -9916,7 +9960,7 @@
       </c>
       <c r="I49" s="8"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50" s="8" t="s">
         <v>550</v>
       </c>
@@ -9943,7 +9987,7 @@
       </c>
       <c r="I50" s="8"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51" s="8" t="s">
         <v>550</v>
       </c>
@@ -9970,7 +10014,7 @@
       </c>
       <c r="I51" s="8"/>
     </row>
-    <row r="52" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="52" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A52" s="48" t="s">
         <v>550</v>
       </c>
@@ -9999,7 +10043,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="53" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A53" s="52" t="s">
         <v>552</v>
       </c>
@@ -10016,7 +10060,7 @@
       <c r="H53" s="10"/>
       <c r="I53" s="10"/>
     </row>
-    <row r="54" spans="1:9" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="54" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A54" s="10" t="s">
         <v>552</v>
       </c>
@@ -10033,7 +10077,7 @@
       <c r="H54" s="10"/>
       <c r="I54" s="10"/>
     </row>
-    <row r="55" spans="1:9" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="55" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A55" s="52" t="s">
         <v>552</v>
       </c>
@@ -10052,7 +10096,7 @@
       <c r="H55" s="10"/>
       <c r="I55" s="10"/>
     </row>
-    <row r="56" spans="1:9" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="56" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A56" s="10" t="s">
         <v>552</v>
       </c>
@@ -10071,7 +10115,7 @@
       <c r="H56" s="10"/>
       <c r="I56" s="10"/>
     </row>
-    <row r="57" spans="1:9" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="57" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A57" s="52" t="s">
         <v>552</v>
       </c>
@@ -10092,7 +10136,7 @@
       <c r="H57" s="10"/>
       <c r="I57" s="10"/>
     </row>
-    <row r="58" spans="1:9" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="58" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A58" s="10" t="s">
         <v>552</v>
       </c>
@@ -10113,7 +10157,7 @@
       <c r="H58" s="10"/>
       <c r="I58" s="10"/>
     </row>
-    <row r="59" spans="1:9" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="59" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A59" s="52" t="s">
         <v>552</v>
       </c>
@@ -10136,7 +10180,7 @@
       <c r="H59" s="10"/>
       <c r="I59" s="10"/>
     </row>
-    <row r="60" spans="1:9" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:9" ht="17.5" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A60" s="10" t="s">
         <v>552</v>
       </c>
@@ -10159,7 +10203,7 @@
       <c r="H60" s="10"/>
       <c r="I60" s="10"/>
     </row>
-    <row r="61" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="61" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A61" s="10" t="s">
         <v>552</v>
       </c>
@@ -10182,7 +10226,7 @@
       <c r="H61" s="10"/>
       <c r="I61" s="10"/>
     </row>
-    <row r="62" spans="1:9" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="62" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A62" s="52" t="s">
         <v>552</v>
       </c>
@@ -10207,7 +10251,7 @@
       <c r="H62" s="10"/>
       <c r="I62" s="10"/>
     </row>
-    <row r="63" spans="1:9" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="63" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A63" s="10" t="s">
         <v>552</v>
       </c>
@@ -10232,7 +10276,7 @@
       <c r="H63" s="10"/>
       <c r="I63" s="10"/>
     </row>
-    <row r="64" spans="1:9" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="64" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A64" s="52" t="s">
         <v>552</v>
       </c>
@@ -10259,7 +10303,7 @@
       </c>
       <c r="I64" s="10"/>
     </row>
-    <row r="65" spans="1:9" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
+    <row r="65" spans="1:9" ht="17.5" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A65" s="10" t="s">
         <v>552</v>
       </c>
@@ -10286,7 +10330,7 @@
       </c>
       <c r="I65" s="10"/>
     </row>
-    <row r="66" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="66" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A66" s="10" t="s">
         <v>552</v>
       </c>
@@ -10313,7 +10357,7 @@
       </c>
       <c r="I66" s="10"/>
     </row>
-    <row r="67" spans="1:9" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="67" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A67" s="52" t="s">
         <v>552</v>
       </c>
@@ -10342,7 +10386,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
+    <row r="68" spans="1:9" ht="17.5" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A68" s="79" t="s">
         <v>116</v>
       </c>
@@ -10371,7 +10415,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A69" s="48" t="s">
         <v>554</v>
       </c>
@@ -10388,7 +10432,7 @@
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A70" s="8" t="s">
         <v>554</v>
       </c>
@@ -10405,7 +10449,7 @@
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A71" s="48" t="s">
         <v>554</v>
       </c>
@@ -10424,7 +10468,7 @@
       <c r="H71" s="48"/>
       <c r="I71" s="48"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A72" s="8" t="s">
         <v>554</v>
       </c>
@@ -10443,7 +10487,7 @@
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A73" s="48" t="s">
         <v>554</v>
       </c>
@@ -10464,7 +10508,7 @@
       <c r="H73" s="48"/>
       <c r="I73" s="48"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A74" s="8" t="s">
         <v>554</v>
       </c>
@@ -10485,7 +10529,7 @@
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A75" s="48" t="s">
         <v>554</v>
       </c>
@@ -10508,7 +10552,7 @@
       <c r="H75" s="48"/>
       <c r="I75" s="48"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A76" s="8" t="s">
         <v>554</v>
       </c>
@@ -10531,7 +10575,7 @@
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A77" s="8" t="s">
         <v>554</v>
       </c>
@@ -10554,7 +10598,7 @@
       <c r="H77" s="8"/>
       <c r="I77" s="8"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A78" s="48" t="s">
         <v>554</v>
       </c>
@@ -10579,7 +10623,7 @@
       <c r="H78" s="48"/>
       <c r="I78" s="48"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A79" s="8" t="s">
         <v>554</v>
       </c>
@@ -10604,7 +10648,7 @@
       <c r="H79" s="8"/>
       <c r="I79" s="8"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A80" s="48" t="s">
         <v>554</v>
       </c>
@@ -10631,7 +10675,7 @@
       </c>
       <c r="I80" s="48"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A81" s="8" t="s">
         <v>554</v>
       </c>
@@ -10658,7 +10702,7 @@
       </c>
       <c r="I81" s="8"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A82" s="8" t="s">
         <v>554</v>
       </c>
@@ -10685,7 +10729,7 @@
       </c>
       <c r="I82" s="8"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A83" s="48" t="s">
         <v>554</v>
       </c>
@@ -10723,7 +10767,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01499B02-9FBB-49DC-B716-A15443742249}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10733,56 +10777,56 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D393B69-42FB-418E-A7B0-B7F239AB871C}">
   <dimension ref="A2:K27"/>
-  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.5625" style="1"/>
+    <col min="1" max="1" width="8.58203125" style="1"/>
     <col min="2" max="2" width="18.25" style="1" customWidth="1"/>
     <col min="3" max="3" width="58.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="61.5625" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.5625" style="1"/>
+    <col min="4" max="4" width="61.58203125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.58203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:11" ht="36" x14ac:dyDescent="0.45">
       <c r="A2" s="14" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="123.4" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B4" s="134" t="s">
+    <row r="4" spans="1:11" ht="123.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="136" t="s">
         <v>522</v>
       </c>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="C4" s="136"/>
+      <c r="D4" s="136"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="121.15" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="134" t="s">
+    <row r="7" spans="1:11" ht="121.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="136" t="s">
         <v>524</v>
       </c>
-      <c r="C7" s="134"/>
-      <c r="D7" s="134"/>
-    </row>
-    <row r="9" spans="1:11" ht="34.9" x14ac:dyDescent="0.6">
+      <c r="C7" s="136"/>
+      <c r="D7" s="136"/>
+    </row>
+    <row r="9" spans="1:11" ht="36" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="17"/>
       <c r="B10" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B11" s="5" t="s">
         <v>70</v>
       </c>
@@ -10793,7 +10837,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="270" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:11" ht="272" x14ac:dyDescent="0.45">
       <c r="B12" s="8" t="s">
         <v>418</v>
       </c>
@@ -10804,7 +10848,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="50.65" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:11" ht="51" x14ac:dyDescent="0.45">
       <c r="B13" s="8" t="s">
         <v>412</v>
       </c>
@@ -10815,7 +10859,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:11" ht="34" x14ac:dyDescent="0.45">
       <c r="B14" s="8" t="s">
         <v>413</v>
       </c>
@@ -10826,7 +10870,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B15" s="8" t="s">
         <v>414</v>
       </c>
@@ -10835,7 +10879,7 @@
       </c>
       <c r="D15" s="9"/>
     </row>
-    <row r="16" spans="1:11" ht="101.25" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:11" ht="102" x14ac:dyDescent="0.45">
       <c r="B16" s="18" t="s">
         <v>513</v>
       </c>
@@ -10847,7 +10891,7 @@
       </c>
       <c r="K16" s="61"/>
     </row>
-    <row r="17" spans="2:4" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:4" ht="34" x14ac:dyDescent="0.45">
       <c r="B17" s="8" t="s">
         <v>8</v>
       </c>
@@ -10858,7 +10902,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:4" ht="34" x14ac:dyDescent="0.45">
       <c r="B18" s="18" t="s">
         <v>7</v>
       </c>
@@ -10869,7 +10913,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:4" ht="34" x14ac:dyDescent="0.45">
       <c r="B19" s="8" t="s">
         <v>75</v>
       </c>
@@ -10880,7 +10924,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B20" s="8" t="s">
         <v>4</v>
       </c>
@@ -10891,19 +10935,19 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
       <c r="D21" s="20"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B22" s="50" t="s">
         <v>525</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="20"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B23" s="5" t="s">
         <v>70</v>
       </c>
@@ -10914,7 +10958,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B24" s="8" t="s">
         <v>526</v>
       </c>
@@ -10925,7 +10969,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:4" ht="34" x14ac:dyDescent="0.45">
       <c r="B25" s="8" t="s">
         <v>529</v>
       </c>
@@ -10936,7 +10980,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B26" s="8" t="s">
         <v>532</v>
       </c>
@@ -10947,7 +10991,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="27" spans="2:4" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:4" ht="34" x14ac:dyDescent="0.45">
       <c r="B27" s="8" t="s">
         <v>535</v>
       </c>
@@ -10973,69 +11017,69 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9341E2BE-4112-4ED2-963F-F03823D626A5}">
   <dimension ref="A2:S48"/>
-  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.5625" style="1"/>
-    <col min="2" max="7" width="15.5625" style="1" customWidth="1"/>
-    <col min="8" max="9" width="16.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.58203125" style="1"/>
+    <col min="2" max="7" width="15.58203125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="20.3125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="21" width="15.5625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.5625" style="1"/>
+    <col min="11" max="11" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="21" width="15.58203125" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.58203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:9" ht="36" x14ac:dyDescent="0.45">
       <c r="A2" s="14" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="198" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B3" s="134" t="s">
+    <row r="3" spans="1:9" ht="198" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="136" t="s">
         <v>591</v>
       </c>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
       <c r="I3" s="20"/>
     </row>
-    <row r="5" spans="1:9" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:9" ht="36" x14ac:dyDescent="0.45">
       <c r="A5" s="14" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="260" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B6" s="134" t="s">
+    <row r="6" spans="1:9" ht="260" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="136" t="s">
         <v>516</v>
       </c>
-      <c r="C6" s="134"/>
-      <c r="D6" s="134"/>
-      <c r="E6" s="134"/>
-      <c r="F6" s="134"/>
-      <c r="G6" s="134"/>
-      <c r="H6" s="134"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
       <c r="I6" s="20"/>
     </row>
-    <row r="8" spans="1:9" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:9" ht="36" x14ac:dyDescent="0.45">
       <c r="A8" s="14" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="145.15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:9" ht="145.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14"/>
-      <c r="B9" s="134" t="s">
+      <c r="B9" s="136" t="s">
         <v>732</v>
       </c>
-      <c r="C9" s="134"/>
-      <c r="D9" s="134"/>
-      <c r="E9" s="134"/>
-      <c r="F9" s="134"/>
-      <c r="G9" s="134"/>
-      <c r="H9" s="134"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="C9" s="136"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="136"/>
+      <c r="F9" s="136"/>
+      <c r="G9" s="136"/>
+      <c r="H9" s="136"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B11" s="97" t="s">
         <v>466</v>
       </c>
@@ -11049,7 +11093,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B12" s="97"/>
       <c r="C12" s="48">
         <v>1</v>
@@ -11061,7 +11105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:9" ht="34" x14ac:dyDescent="0.45">
       <c r="B14" s="99" t="s">
         <v>467</v>
       </c>
@@ -11075,7 +11119,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B15" s="97" t="s">
         <v>549</v>
       </c>
@@ -11089,7 +11133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B16" s="97" t="s">
         <v>550</v>
       </c>
@@ -11103,7 +11147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B17" s="97" t="s">
         <v>551</v>
       </c>
@@ -11117,7 +11161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B18" s="97" t="s">
         <v>552</v>
       </c>
@@ -11131,7 +11175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B19" s="97" t="s">
         <v>554</v>
       </c>
@@ -11145,29 +11189,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:19" ht="36" x14ac:dyDescent="0.45">
       <c r="A21" s="14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="305.2" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B22" s="134" t="s">
+    <row r="22" spans="1:19" ht="305.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="136" t="s">
         <v>538</v>
       </c>
-      <c r="C22" s="134"/>
-      <c r="D22" s="134"/>
-      <c r="E22" s="134"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="134"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="136"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="136"/>
+      <c r="H22" s="136"/>
       <c r="I22" s="20"/>
     </row>
-    <row r="24" spans="1:19" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:19" ht="36" x14ac:dyDescent="0.45">
       <c r="A24" s="14" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:19" ht="36" x14ac:dyDescent="0.45">
       <c r="A25" s="14"/>
       <c r="F25" s="4">
         <v>4</v>
@@ -11179,7 +11223,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="50.65" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:19" ht="51" x14ac:dyDescent="0.45">
       <c r="B26" s="5" t="s">
         <v>458</v>
       </c>
@@ -11214,7 +11258,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B27" s="8">
         <v>1</v>
       </c>
@@ -11250,7 +11294,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B28" s="8">
         <v>2</v>
       </c>
@@ -11275,7 +11319,7 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B29" s="51">
         <v>3</v>
       </c>
@@ -11302,7 +11346,7 @@
       </c>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B30" s="8">
         <v>4</v>
       </c>
@@ -11337,7 +11381,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B31" s="51">
         <v>5</v>
       </c>
@@ -11364,7 +11408,7 @@
       </c>
       <c r="L31" s="6"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B32" s="8">
         <v>6</v>
       </c>
@@ -11389,7 +11433,7 @@
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B33" s="51">
         <v>7</v>
       </c>
@@ -11424,7 +11468,7 @@
       </c>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B34" s="8">
         <v>8</v>
       </c>
@@ -11451,7 +11495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="35" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B35" s="8">
         <v>9</v>
       </c>
@@ -11476,7 +11520,7 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="36" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B36" s="51">
         <v>10</v>
       </c>
@@ -11511,7 +11555,7 @@
       </c>
       <c r="L36" s="6"/>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B37" s="8">
         <v>11</v>
       </c>
@@ -11538,7 +11582,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B38" s="51">
         <v>12</v>
       </c>
@@ -11568,7 +11612,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B39" s="101">
         <v>13</v>
       </c>
@@ -11601,7 +11645,7 @@
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
     </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B40" s="8">
         <v>14</v>
       </c>
@@ -11628,7 +11672,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="41" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B41" s="51">
         <v>15</v>
       </c>
@@ -11655,7 +11699,7 @@
       </c>
       <c r="L41" s="6"/>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B42" s="3" t="s">
         <v>21</v>
       </c>
@@ -11676,7 +11720,7 @@
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.6">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.45">
       <c r="R48" s="1" t="s">
         <v>559</v>
       </c>
@@ -11703,28 +11747,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D54D80AB-3F8B-4848-807B-3D7386D79971}">
   <dimension ref="A2:I105"/>
-  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.5625" style="1"/>
+    <col min="1" max="1" width="8.58203125" style="1"/>
     <col min="2" max="2" width="25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5625" style="1"/>
-    <col min="5" max="5" width="120.8125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5625" style="1"/>
-    <col min="7" max="7" width="9.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.58203125" style="1"/>
+    <col min="5" max="5" width="120.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.58203125" style="1"/>
+    <col min="7" max="7" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.5625" style="1"/>
+    <col min="12" max="16384" width="8.58203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.45">
       <c r="A2" s="14" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B3" s="5" t="s">
         <v>90</v>
       </c>
@@ -11738,7 +11782,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B4" s="28" t="s">
         <v>102</v>
       </c>
@@ -11752,7 +11796,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B5" s="28" t="s">
         <v>106</v>
       </c>
@@ -11766,7 +11810,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B6" s="28" t="s">
         <v>540</v>
       </c>
@@ -11780,7 +11824,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B7" s="8" t="s">
         <v>43</v>
       </c>
@@ -11794,7 +11838,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B8" s="8" t="s">
         <v>120</v>
       </c>
@@ -11808,7 +11852,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:5" ht="34" x14ac:dyDescent="0.45">
       <c r="B9" s="8" t="s">
         <v>89</v>
       </c>
@@ -11822,7 +11866,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:5" ht="34" x14ac:dyDescent="0.45">
       <c r="B10" s="8" t="s">
         <v>44</v>
       </c>
@@ -11836,12 +11880,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.45">
       <c r="A12" s="14" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.45">
       <c r="A13" s="14"/>
       <c r="B13" s="5" t="s">
         <v>90</v>
@@ -11856,7 +11900,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B14" s="8" t="s">
         <v>450</v>
       </c>
@@ -11870,7 +11914,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B15" s="8" t="s">
         <v>413</v>
       </c>
@@ -11884,7 +11928,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B16" s="8" t="s">
         <v>414</v>
       </c>
@@ -11898,7 +11942,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B17" s="8" t="s">
         <v>8</v>
       </c>
@@ -11912,7 +11956,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B18" s="8" t="s">
         <v>7</v>
       </c>
@@ -11926,7 +11970,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B19" s="8" t="s">
         <v>99</v>
       </c>
@@ -11940,7 +11984,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B20" s="8" t="s">
         <v>4</v>
       </c>
@@ -11954,12 +11998,12 @@
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
     </row>
-    <row r="22" spans="1:9" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:9" ht="36" x14ac:dyDescent="0.45">
       <c r="A22" s="14" t="s">
         <v>194</v>
       </c>
@@ -11968,7 +12012,7 @@
       <c r="D22" s="30"/>
       <c r="E22" s="17"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B23" s="5" t="s">
         <v>90</v>
       </c>
@@ -11982,7 +12026,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B24" s="8" t="s">
         <v>12</v>
       </c>
@@ -11996,7 +12040,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B25" s="8" t="s">
         <v>203</v>
       </c>
@@ -12010,7 +12054,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B26" s="8" t="s">
         <v>496</v>
       </c>
@@ -12024,7 +12068,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:9" ht="68" x14ac:dyDescent="0.45">
       <c r="B27" s="8" t="s">
         <v>206</v>
       </c>
@@ -12038,7 +12082,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="84.4" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:9" ht="85" x14ac:dyDescent="0.45">
       <c r="B28" s="8" t="s">
         <v>295</v>
       </c>
@@ -12052,7 +12096,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:9" ht="51" x14ac:dyDescent="0.45">
       <c r="B29" s="8" t="s">
         <v>299</v>
       </c>
@@ -12075,7 +12119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B30" s="8" t="s">
         <v>306</v>
       </c>
@@ -12098,7 +12142,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:9" ht="34" x14ac:dyDescent="0.45">
       <c r="B31" s="8" t="s">
         <v>860</v>
       </c>
@@ -12121,7 +12165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:9" ht="34" x14ac:dyDescent="0.45">
       <c r="B32" s="8" t="s">
         <v>861</v>
       </c>
@@ -12141,7 +12185,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B33" s="8" t="s">
         <v>484</v>
       </c>
@@ -12155,12 +12199,12 @@
         <v>485</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:5" ht="36" x14ac:dyDescent="0.45">
       <c r="A35" s="14" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B36" s="5" t="s">
         <v>90</v>
       </c>
@@ -12174,7 +12218,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B37" s="101" t="s">
         <v>102</v>
       </c>
@@ -12188,7 +12232,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B38" s="101" t="s">
         <v>475</v>
       </c>
@@ -12202,7 +12246,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B39" s="101" t="s">
         <v>116</v>
       </c>
@@ -12216,7 +12260,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="40" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B40" s="28" t="s">
         <v>154</v>
       </c>
@@ -12230,7 +12274,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="17.649999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="41" spans="1:5" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B41" s="52" t="s">
         <v>856</v>
       </c>
@@ -12244,15 +12288,15 @@
         <v>487</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
-      <c r="B42" s="135" t="s">
+    <row r="42" spans="1:5" ht="17.5" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B42" s="141" t="s">
         <v>184</v>
       </c>
-      <c r="C42" s="136"/>
-      <c r="D42" s="136"/>
-      <c r="E42" s="136"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="C42" s="142"/>
+      <c r="D42" s="142"/>
+      <c r="E42" s="142"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B43" s="8" t="s">
         <v>148</v>
       </c>
@@ -12266,7 +12310,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B44" s="8" t="s">
         <v>149</v>
       </c>
@@ -12280,7 +12324,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B45" s="8" t="s">
         <v>726</v>
       </c>
@@ -12294,7 +12338,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B46" s="8" t="s">
         <v>727</v>
       </c>
@@ -12308,7 +12352,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B47" s="8" t="s">
         <v>728</v>
       </c>
@@ -12322,7 +12366,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B48" s="8" t="s">
         <v>711</v>
       </c>
@@ -12336,7 +12380,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B49" s="8" t="s">
         <v>710</v>
       </c>
@@ -12350,7 +12394,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B50" s="8" t="s">
         <v>709</v>
       </c>
@@ -12364,17 +12408,17 @@
         <v>714</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
       <c r="D51" s="16"/>
     </row>
-    <row r="52" spans="1:5" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:5" ht="36" x14ac:dyDescent="0.45">
       <c r="A52" s="14" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="53" spans="1:5" ht="36" x14ac:dyDescent="0.45">
       <c r="A53" s="14"/>
       <c r="B53" s="5" t="s">
         <v>90</v>
@@ -12389,7 +12433,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B54" s="28" t="s">
         <v>106</v>
       </c>
@@ -12403,7 +12447,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B55" s="28" t="s">
         <v>114</v>
       </c>
@@ -12417,7 +12461,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B56" s="28" t="s">
         <v>171</v>
       </c>
@@ -12431,15 +12475,15 @@
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="B57" s="135" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B57" s="141" t="s">
         <v>184</v>
       </c>
-      <c r="C57" s="136"/>
-      <c r="D57" s="136"/>
-      <c r="E57" s="136"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="C57" s="142"/>
+      <c r="D57" s="142"/>
+      <c r="E57" s="142"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B58" s="28" t="s">
         <v>190</v>
       </c>
@@ -12453,7 +12497,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B59" s="28" t="s">
         <v>198</v>
       </c>
@@ -12465,15 +12509,15 @@
       </c>
       <c r="E59" s="29"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="B60" s="137" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B60" s="143" t="s">
         <v>193</v>
       </c>
-      <c r="C60" s="137"/>
-      <c r="D60" s="137"/>
-      <c r="E60" s="137"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="C60" s="143"/>
+      <c r="D60" s="143"/>
+      <c r="E60" s="143"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B61" s="28" t="s">
         <v>191</v>
       </c>
@@ -12487,7 +12531,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B62" s="44" t="s">
         <v>199</v>
       </c>
@@ -12499,15 +12543,15 @@
       </c>
       <c r="E62" s="29"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="B63" s="137" t="s">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B63" s="143" t="s">
         <v>192</v>
       </c>
-      <c r="C63" s="137"/>
-      <c r="D63" s="137"/>
-      <c r="E63" s="137"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="C63" s="143"/>
+      <c r="D63" s="143"/>
+      <c r="E63" s="143"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B64" s="28" t="s">
         <v>187</v>
       </c>
@@ -12519,7 +12563,7 @@
       </c>
       <c r="E64" s="29"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B65" s="28" t="s">
         <v>275</v>
       </c>
@@ -12531,7 +12575,7 @@
       </c>
       <c r="E65" s="29"/>
     </row>
-    <row r="66" spans="1:5" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="66" spans="1:5" ht="34" x14ac:dyDescent="0.45">
       <c r="B66" s="28" t="s">
         <v>277</v>
       </c>
@@ -12545,7 +12589,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B67" s="28" t="s">
         <v>278</v>
       </c>
@@ -12559,7 +12603,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B68" s="28" t="s">
         <v>279</v>
       </c>
@@ -12573,13 +12617,13 @@
         <v>283</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B69" s="94"/>
       <c r="C69" s="94"/>
       <c r="D69" s="94"/>
       <c r="E69" s="95"/>
     </row>
-    <row r="70" spans="1:5" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="70" spans="1:5" ht="36" x14ac:dyDescent="0.45">
       <c r="A70" s="14" t="s">
         <v>541</v>
       </c>
@@ -12588,7 +12632,7 @@
       <c r="D70" s="94"/>
       <c r="E70" s="95"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B71" s="92" t="s">
         <v>90</v>
       </c>
@@ -12602,7 +12646,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="72" spans="1:5" ht="34" x14ac:dyDescent="0.45">
       <c r="B72" s="104" t="s">
         <v>398</v>
       </c>
@@ -12616,7 +12660,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="67.5" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:5" ht="68" x14ac:dyDescent="0.45">
       <c r="B73" s="90" t="s">
         <v>583</v>
       </c>
@@ -12630,7 +12674,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:5" ht="34" x14ac:dyDescent="0.45">
       <c r="B74" s="120" t="s">
         <v>582</v>
       </c>
@@ -12644,7 +12688,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="75" spans="1:5" ht="51" x14ac:dyDescent="0.45">
       <c r="B75" s="90" t="s">
         <v>581</v>
       </c>
@@ -12658,7 +12702,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="50.65" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:5" ht="51" x14ac:dyDescent="0.45">
       <c r="B76" s="119" t="s">
         <v>561</v>
       </c>
@@ -12672,7 +12716,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:5" ht="34" x14ac:dyDescent="0.45">
       <c r="B77" s="117" t="s">
         <v>579</v>
       </c>
@@ -12686,7 +12730,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B78" s="90" t="s">
         <v>580</v>
       </c>
@@ -12700,7 +12744,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B79" s="107" t="s">
         <v>410</v>
       </c>
@@ -12714,18 +12758,18 @@
         <v>546</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B80" s="30"/>
       <c r="C80" s="30"/>
       <c r="D80" s="30"/>
       <c r="E80" s="17"/>
     </row>
-    <row r="81" spans="1:5" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="81" spans="1:5" ht="36" x14ac:dyDescent="0.45">
       <c r="A81" s="14" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B82" s="5" t="s">
         <v>90</v>
       </c>
@@ -12739,7 +12783,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B83" s="8" t="s">
         <v>43</v>
       </c>
@@ -12753,7 +12797,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B84" s="8" t="s">
         <v>130</v>
       </c>
@@ -12767,7 +12811,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B85" s="8" t="s">
         <v>123</v>
       </c>
@@ -12779,7 +12823,7 @@
       </c>
       <c r="E85" s="2"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B86" s="8" t="s">
         <v>31</v>
       </c>
@@ -12791,7 +12835,7 @@
       </c>
       <c r="E86" s="2"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B87" s="8" t="s">
         <v>33</v>
       </c>
@@ -12803,20 +12847,20 @@
       </c>
       <c r="E87" s="2"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="B88" s="135" t="s">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B88" s="141" t="s">
         <v>201</v>
       </c>
-      <c r="C88" s="136"/>
-      <c r="D88" s="136"/>
-      <c r="E88" s="136"/>
-    </row>
-    <row r="90" spans="1:5" ht="34.9" x14ac:dyDescent="0.6">
+      <c r="C88" s="142"/>
+      <c r="D88" s="142"/>
+      <c r="E88" s="142"/>
+    </row>
+    <row r="90" spans="1:5" ht="36" x14ac:dyDescent="0.45">
       <c r="A90" s="14" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B91" s="5" t="s">
         <v>90</v>
       </c>
@@ -12830,7 +12874,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="92" spans="1:5" ht="34" x14ac:dyDescent="0.45">
       <c r="B92" s="8" t="s">
         <v>89</v>
       </c>
@@ -12844,7 +12888,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B93" s="8" t="s">
         <v>84</v>
       </c>
@@ -12856,7 +12900,7 @@
       </c>
       <c r="E93" s="2"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B94" s="8" t="s">
         <v>131</v>
       </c>
@@ -12868,7 +12912,7 @@
       </c>
       <c r="E94" s="2"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B95" s="8" t="s">
         <v>862</v>
       </c>
@@ -12880,7 +12924,7 @@
       </c>
       <c r="E95" s="2"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B96" s="8" t="s">
         <v>863</v>
       </c>
@@ -12892,7 +12936,7 @@
       </c>
       <c r="E96" s="2"/>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B97" s="8" t="s">
         <v>864</v>
       </c>
@@ -12904,7 +12948,7 @@
       </c>
       <c r="E97" s="2"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B98" s="8" t="s">
         <v>142</v>
       </c>
@@ -12918,7 +12962,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B99" s="8" t="s">
         <v>143</v>
       </c>
@@ -12932,7 +12976,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B100" s="8" t="s">
         <v>144</v>
       </c>
@@ -12946,7 +12990,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B101" s="8" t="s">
         <v>145</v>
       </c>
@@ -12958,7 +13002,7 @@
       </c>
       <c r="E101" s="15"/>
     </row>
-    <row r="102" spans="2:5" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="102" spans="2:5" ht="34" x14ac:dyDescent="0.45">
       <c r="B102" s="8" t="s">
         <v>44</v>
       </c>
@@ -12972,7 +13016,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B103" s="8" t="s">
         <v>86</v>
       </c>
@@ -12984,7 +13028,7 @@
       </c>
       <c r="E103" s="2"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B104" s="8" t="s">
         <v>87</v>
       </c>
@@ -12996,13 +13040,13 @@
       </c>
       <c r="E104" s="2"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B105" s="135" t="s">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B105" s="141" t="s">
         <v>202</v>
       </c>
-      <c r="C105" s="136"/>
-      <c r="D105" s="136"/>
-      <c r="E105" s="136"/>
+      <c r="C105" s="142"/>
+      <c r="D105" s="142"/>
+      <c r="E105" s="142"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -13021,1557 +13065,1653 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49EADB8A-A56B-4172-9C74-8340E2A91FD9}">
-  <dimension ref="A1:BI7"/>
-  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:BJ18"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.5625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="15.3125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="32.9375" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="16.5625" style="8" customWidth="1"/>
-    <col min="8" max="11" width="12.5625" style="8" customWidth="1"/>
-    <col min="12" max="13" width="50.5625" style="8" customWidth="1"/>
-    <col min="14" max="14" width="20.6875" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.5625" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="61" width="20.5625" style="8" customWidth="1"/>
-    <col min="62" max="16384" width="8.5625" style="16"/>
+    <col min="1" max="1" width="8.58203125" style="16"/>
+    <col min="2" max="2" width="12.58203125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.58203125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="32.9140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="16.58203125" style="8" customWidth="1"/>
+    <col min="9" max="12" width="12.58203125" style="8" customWidth="1"/>
+    <col min="13" max="14" width="50.58203125" style="8" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="18.58203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="62" width="20.58203125" style="8" customWidth="1"/>
+    <col min="63" max="16384" width="8.58203125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="B1" s="131" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>870</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>872</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>872</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>872</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>873</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>873</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>874</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="2" spans="1:62" ht="34" x14ac:dyDescent="0.45">
+      <c r="A2" s="8" t="s">
+        <v>868</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="130" t="s">
+      <c r="C2" s="130" t="s">
         <v>837</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="N1" s="124" t="s">
+      <c r="O2" s="124" t="s">
         <v>729</v>
       </c>
-      <c r="O1" s="124" t="s">
+      <c r="P2" s="124" t="s">
         <v>730</v>
       </c>
-      <c r="P1" s="124" t="s">
+      <c r="Q2" s="124" t="s">
         <v>731</v>
       </c>
-      <c r="Q1" s="116" t="s">
+      <c r="R2" s="116" t="s">
         <v>614</v>
       </c>
-      <c r="R1" s="116" t="s">
+      <c r="S2" s="116" t="s">
         <v>616</v>
       </c>
-      <c r="S1" s="116" t="s">
+      <c r="T2" s="116" t="s">
         <v>617</v>
       </c>
-      <c r="T1" s="116" t="s">
+      <c r="U2" s="116" t="s">
         <v>618</v>
       </c>
-      <c r="U1" s="116" t="s">
+      <c r="V2" s="116" t="s">
         <v>619</v>
       </c>
-      <c r="V1" s="116" t="s">
+      <c r="W2" s="116" t="s">
         <v>620</v>
       </c>
-      <c r="W1" s="116" t="s">
+      <c r="X2" s="116" t="s">
         <v>621</v>
       </c>
-      <c r="X1" s="116" t="s">
+      <c r="Y2" s="116" t="s">
         <v>622</v>
       </c>
-      <c r="Y1" s="116" t="s">
+      <c r="Z2" s="116" t="s">
         <v>623</v>
       </c>
-      <c r="Z1" s="116" t="s">
+      <c r="AA2" s="116" t="s">
         <v>624</v>
       </c>
-      <c r="AA1" s="116" t="s">
+      <c r="AB2" s="116" t="s">
         <v>625</v>
       </c>
-      <c r="AB1" s="116" t="s">
+      <c r="AC2" s="116" t="s">
         <v>626</v>
       </c>
-      <c r="AC1" s="116" t="s">
+      <c r="AD2" s="116" t="s">
         <v>627</v>
       </c>
-      <c r="AD1" s="116" t="s">
+      <c r="AE2" s="116" t="s">
         <v>628</v>
       </c>
-      <c r="AE1" s="116" t="s">
+      <c r="AF2" s="116" t="s">
         <v>629</v>
       </c>
-      <c r="AF1" s="116" t="s">
+      <c r="AG2" s="116" t="s">
         <v>615</v>
       </c>
-      <c r="AG1" s="116" t="s">
+      <c r="AH2" s="116" t="s">
         <v>648</v>
       </c>
-      <c r="AH1" s="116" t="s">
+      <c r="AI2" s="116" t="s">
         <v>650</v>
       </c>
-      <c r="AI1" s="116" t="s">
+      <c r="AJ2" s="116" t="s">
         <v>651</v>
       </c>
-      <c r="AJ1" s="116" t="s">
+      <c r="AK2" s="116" t="s">
         <v>652</v>
       </c>
-      <c r="AK1" s="116" t="s">
+      <c r="AL2" s="116" t="s">
         <v>653</v>
       </c>
-      <c r="AL1" s="116" t="s">
+      <c r="AM2" s="116" t="s">
         <v>654</v>
       </c>
-      <c r="AM1" s="116" t="s">
+      <c r="AN2" s="116" t="s">
         <v>655</v>
       </c>
-      <c r="AN1" s="116" t="s">
+      <c r="AO2" s="116" t="s">
         <v>656</v>
       </c>
-      <c r="AO1" s="116" t="s">
+      <c r="AP2" s="116" t="s">
         <v>657</v>
       </c>
-      <c r="AP1" s="116" t="s">
+      <c r="AQ2" s="116" t="s">
         <v>658</v>
       </c>
-      <c r="AQ1" s="116" t="s">
+      <c r="AR2" s="116" t="s">
         <v>659</v>
       </c>
-      <c r="AR1" s="116" t="s">
+      <c r="AS2" s="116" t="s">
         <v>660</v>
       </c>
-      <c r="AS1" s="116" t="s">
+      <c r="AT2" s="116" t="s">
         <v>661</v>
       </c>
-      <c r="AT1" s="116" t="s">
+      <c r="AU2" s="116" t="s">
         <v>662</v>
       </c>
-      <c r="AU1" s="116" t="s">
+      <c r="AV2" s="116" t="s">
         <v>645</v>
       </c>
-      <c r="AV1" s="116" t="s">
+      <c r="AW2" s="116" t="s">
         <v>676</v>
       </c>
-      <c r="AW1" s="116" t="s">
+      <c r="AX2" s="116" t="s">
         <v>678</v>
       </c>
-      <c r="AX1" s="116" t="s">
+      <c r="AY2" s="116" t="s">
         <v>679</v>
       </c>
-      <c r="AY1" s="116" t="s">
+      <c r="AZ2" s="116" t="s">
         <v>680</v>
       </c>
-      <c r="AZ1" s="116" t="s">
+      <c r="BA2" s="116" t="s">
         <v>681</v>
       </c>
-      <c r="BA1" s="116" t="s">
+      <c r="BB2" s="116" t="s">
         <v>682</v>
       </c>
-      <c r="BB1" s="116" t="s">
+      <c r="BC2" s="116" t="s">
         <v>683</v>
       </c>
-      <c r="BC1" s="116" t="s">
+      <c r="BD2" s="116" t="s">
         <v>684</v>
       </c>
-      <c r="BD1" s="116" t="s">
+      <c r="BE2" s="116" t="s">
         <v>685</v>
       </c>
-      <c r="BE1" s="116" t="s">
+      <c r="BF2" s="116" t="s">
         <v>686</v>
       </c>
-      <c r="BF1" s="116" t="s">
+      <c r="BG2" s="116" t="s">
         <v>687</v>
       </c>
-      <c r="BG1" s="116" t="s">
+      <c r="BH2" s="116" t="s">
         <v>688</v>
       </c>
-      <c r="BH1" s="116" t="s">
+      <c r="BI2" s="116" t="s">
         <v>689</v>
       </c>
-      <c r="BI1" s="116" t="s">
+      <c r="BJ2" s="116" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="2" spans="1:61" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A2" s="4" t="s">
+    <row r="3" spans="1:62" ht="34" x14ac:dyDescent="0.45">
+      <c r="A3" s="8"/>
+      <c r="B3" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B2" s="129" t="s">
+      <c r="C3" s="129" t="s">
         <v>838</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="N2" s="124" t="s">
+      <c r="O3" s="124" t="s">
         <v>733</v>
       </c>
-      <c r="O2" s="124" t="s">
+      <c r="P3" s="124" t="s">
         <v>727</v>
       </c>
-      <c r="P2" s="124" t="s">
+      <c r="Q3" s="124" t="s">
         <v>728</v>
       </c>
-      <c r="Q2" s="116" t="s">
+      <c r="R3" s="116" t="s">
         <v>630</v>
       </c>
-      <c r="R2" s="116" t="s">
+      <c r="S3" s="116" t="s">
         <v>631</v>
       </c>
-      <c r="S2" s="116" t="s">
+      <c r="T3" s="116" t="s">
         <v>632</v>
       </c>
-      <c r="T2" s="116" t="s">
+      <c r="U3" s="116" t="s">
         <v>633</v>
       </c>
-      <c r="U2" s="116" t="s">
+      <c r="V3" s="116" t="s">
         <v>634</v>
       </c>
-      <c r="V2" s="116" t="s">
+      <c r="W3" s="116" t="s">
         <v>635</v>
       </c>
-      <c r="W2" s="116" t="s">
+      <c r="X3" s="116" t="s">
         <v>636</v>
       </c>
-      <c r="X2" s="116" t="s">
+      <c r="Y3" s="116" t="s">
         <v>637</v>
       </c>
-      <c r="Y2" s="116" t="s">
+      <c r="Z3" s="116" t="s">
         <v>638</v>
       </c>
-      <c r="Z2" s="116" t="s">
+      <c r="AA3" s="116" t="s">
         <v>639</v>
       </c>
-      <c r="AA2" s="116" t="s">
+      <c r="AB3" s="116" t="s">
         <v>640</v>
       </c>
-      <c r="AB2" s="116" t="s">
+      <c r="AC3" s="116" t="s">
         <v>641</v>
       </c>
-      <c r="AC2" s="116" t="s">
+      <c r="AD3" s="116" t="s">
         <v>642</v>
       </c>
-      <c r="AD2" s="116" t="s">
+      <c r="AE3" s="116" t="s">
         <v>643</v>
       </c>
-      <c r="AE2" s="116" t="s">
+      <c r="AF3" s="116" t="s">
         <v>644</v>
       </c>
-      <c r="AF2" s="116" t="s">
+      <c r="AG3" s="116" t="s">
         <v>646</v>
       </c>
-      <c r="AG2" s="116" t="s">
+      <c r="AH3" s="116" t="s">
         <v>649</v>
       </c>
-      <c r="AH2" s="116" t="s">
+      <c r="AI3" s="116" t="s">
         <v>663</v>
       </c>
-      <c r="AI2" s="116" t="s">
+      <c r="AJ3" s="116" t="s">
         <v>664</v>
       </c>
-      <c r="AJ2" s="116" t="s">
+      <c r="AK3" s="116" t="s">
         <v>665</v>
       </c>
-      <c r="AK2" s="116" t="s">
+      <c r="AL3" s="116" t="s">
         <v>666</v>
       </c>
-      <c r="AL2" s="116" t="s">
+      <c r="AM3" s="116" t="s">
         <v>667</v>
       </c>
-      <c r="AM2" s="116" t="s">
+      <c r="AN3" s="116" t="s">
         <v>668</v>
       </c>
-      <c r="AN2" s="116" t="s">
+      <c r="AO3" s="116" t="s">
         <v>669</v>
       </c>
-      <c r="AO2" s="116" t="s">
+      <c r="AP3" s="116" t="s">
         <v>670</v>
       </c>
-      <c r="AP2" s="116" t="s">
+      <c r="AQ3" s="116" t="s">
         <v>671</v>
       </c>
-      <c r="AQ2" s="116" t="s">
+      <c r="AR3" s="116" t="s">
         <v>672</v>
       </c>
-      <c r="AR2" s="116" t="s">
+      <c r="AS3" s="116" t="s">
         <v>673</v>
       </c>
-      <c r="AS2" s="116" t="s">
+      <c r="AT3" s="116" t="s">
         <v>674</v>
       </c>
-      <c r="AT2" s="116" t="s">
+      <c r="AU3" s="116" t="s">
         <v>675</v>
       </c>
-      <c r="AU2" s="115" t="s">
+      <c r="AV3" s="115" t="s">
         <v>647</v>
       </c>
-      <c r="AV2" s="115" t="s">
+      <c r="AW3" s="115" t="s">
         <v>677</v>
       </c>
-      <c r="AW2" s="115" t="s">
+      <c r="AX3" s="115" t="s">
         <v>691</v>
       </c>
-      <c r="AX2" s="115" t="s">
+      <c r="AY3" s="115" t="s">
         <v>692</v>
       </c>
-      <c r="AY2" s="115" t="s">
+      <c r="AZ3" s="115" t="s">
         <v>693</v>
       </c>
-      <c r="AZ2" s="115" t="s">
+      <c r="BA3" s="115" t="s">
         <v>694</v>
       </c>
-      <c r="BA2" s="115" t="s">
+      <c r="BB3" s="115" t="s">
         <v>708</v>
       </c>
-      <c r="BB2" s="115" t="s">
+      <c r="BC3" s="115" t="s">
         <v>695</v>
       </c>
-      <c r="BC2" s="115" t="s">
+      <c r="BD3" s="115" t="s">
         <v>696</v>
       </c>
-      <c r="BD2" s="115" t="s">
+      <c r="BE3" s="115" t="s">
         <v>697</v>
       </c>
-      <c r="BE2" s="115" t="s">
+      <c r="BF3" s="115" t="s">
         <v>698</v>
       </c>
-      <c r="BF2" s="115" t="s">
+      <c r="BG3" s="115" t="s">
         <v>699</v>
       </c>
-      <c r="BG2" s="115" t="s">
+      <c r="BH3" s="115" t="s">
         <v>700</v>
       </c>
-      <c r="BH2" s="115" t="s">
+      <c r="BI3" s="115" t="s">
         <v>701</v>
       </c>
-      <c r="BI2" s="115" t="s">
+      <c r="BJ3" s="115" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="3" spans="1:61" x14ac:dyDescent="0.6">
-      <c r="A3" s="8">
+    <row r="4" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="B4" s="8">
         <v>10001</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>839</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>549</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="E4" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="8">
+      <c r="F4" s="8">
         <v>7</v>
       </c>
-      <c r="F3" s="8">
+      <c r="G4" s="8">
         <v>7</v>
       </c>
-      <c r="G3" s="8">
+      <c r="H4" s="8">
         <v>6</v>
       </c>
-      <c r="H3" s="33">
+      <c r="I4" s="33">
         <v>0.1</v>
       </c>
-      <c r="I3" s="33">
+      <c r="J4" s="33">
         <v>0.25</v>
       </c>
-      <c r="J3" s="33">
+      <c r="K4" s="33">
         <v>0.1</v>
       </c>
-      <c r="K3" s="8">
+      <c r="L4" s="8">
         <v>1</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="M4" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="N3" s="63">
+      <c r="O4" s="63">
         <f>'성장 시스템'!$C$12+'성장 시스템'!C15</f>
         <v>3</v>
       </c>
-      <c r="O3" s="63">
+      <c r="P4" s="63">
         <f>'성장 시스템'!$D$12+'성장 시스템'!D15</f>
         <v>2</v>
       </c>
-      <c r="P3" s="63">
+      <c r="Q4" s="63">
         <f>'성장 시스템'!$E$12+'성장 시스템'!E15</f>
         <v>1</v>
       </c>
-      <c r="Q3" s="8">
-        <f>E3</f>
+      <c r="R4" s="8">
+        <f>F4</f>
         <v>7</v>
       </c>
-      <c r="R3" s="8">
-        <f>Q3+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
+      <c r="S4" s="8">
+        <f>R4+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
         <v>10</v>
       </c>
-      <c r="S3" s="8">
-        <f>R3+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
+      <c r="T4" s="8">
+        <f>S4+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
         <v>13</v>
       </c>
-      <c r="T3" s="8">
-        <f>S3+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
+      <c r="U4" s="8">
+        <f>T4+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
         <v>16</v>
       </c>
-      <c r="U3" s="8">
-        <f>T3+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
+      <c r="V4" s="8">
+        <f>U4+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
         <v>19</v>
       </c>
-      <c r="V3" s="8">
-        <f>U3+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
+      <c r="W4" s="8">
+        <f>V4+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
         <v>22</v>
       </c>
-      <c r="W3" s="8">
-        <f>V3+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
+      <c r="X4" s="8">
+        <f>W4+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
         <v>25</v>
       </c>
-      <c r="X3" s="8">
-        <f>W3+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
+      <c r="Y4" s="8">
+        <f>X4+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
         <v>28</v>
       </c>
-      <c r="Y3" s="8">
-        <f>X3+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
+      <c r="Z4" s="8">
+        <f>Y4+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
         <v>31</v>
       </c>
-      <c r="Z3" s="8">
-        <f>Y3+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
+      <c r="AA4" s="8">
+        <f>Z4+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
         <v>34</v>
       </c>
-      <c r="AA3" s="8">
-        <f>Z3+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
+      <c r="AB4" s="8">
+        <f>AA4+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
         <v>37</v>
       </c>
-      <c r="AB3" s="8">
-        <f>AA3+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
+      <c r="AC4" s="8">
+        <f>AB4+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
         <v>40</v>
       </c>
-      <c r="AC3" s="8">
-        <f>AB3+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
+      <c r="AD4" s="8">
+        <f>AC4+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
         <v>43</v>
       </c>
-      <c r="AD3" s="8">
-        <f>AC3+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
+      <c r="AE4" s="8">
+        <f>AD4+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
         <v>46</v>
       </c>
-      <c r="AE3" s="8">
-        <f>AD3+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
+      <c r="AF4" s="8">
+        <f>AE4+'성장 시스템'!$C$12+'성장 시스템'!$C$15</f>
         <v>49</v>
       </c>
-      <c r="AF3" s="8">
-        <f>F3</f>
+      <c r="AG4" s="8">
+        <f>G4</f>
         <v>7</v>
       </c>
-      <c r="AG3" s="8">
-        <f>AF3+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
+      <c r="AH4" s="8">
+        <f>AG4+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
         <v>9</v>
       </c>
-      <c r="AH3" s="8">
-        <f>AG3+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
+      <c r="AI4" s="8">
+        <f>AH4+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
         <v>11</v>
       </c>
-      <c r="AI3" s="8">
-        <f>AH3+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
+      <c r="AJ4" s="8">
+        <f>AI4+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
         <v>13</v>
       </c>
-      <c r="AJ3" s="8">
-        <f>AI3+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
+      <c r="AK4" s="8">
+        <f>AJ4+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
         <v>15</v>
       </c>
-      <c r="AK3" s="8">
-        <f>AJ3+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
+      <c r="AL4" s="8">
+        <f>AK4+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
         <v>17</v>
       </c>
-      <c r="AL3" s="8">
-        <f>AK3+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
+      <c r="AM4" s="8">
+        <f>AL4+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
         <v>19</v>
       </c>
-      <c r="AM3" s="8">
-        <f>AL3+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
+      <c r="AN4" s="8">
+        <f>AM4+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
         <v>21</v>
       </c>
-      <c r="AN3" s="8">
-        <f>AM3+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
+      <c r="AO4" s="8">
+        <f>AN4+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
         <v>23</v>
       </c>
-      <c r="AO3" s="8">
-        <f>AN3+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
+      <c r="AP4" s="8">
+        <f>AO4+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
         <v>25</v>
       </c>
-      <c r="AP3" s="8">
-        <f>AO3+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
+      <c r="AQ4" s="8">
+        <f>AP4+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
         <v>27</v>
       </c>
-      <c r="AQ3" s="8">
-        <f>AP3+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
+      <c r="AR4" s="8">
+        <f>AQ4+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
         <v>29</v>
       </c>
-      <c r="AR3" s="8">
-        <f>AQ3+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
+      <c r="AS4" s="8">
+        <f>AR4+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
         <v>31</v>
       </c>
-      <c r="AS3" s="8">
-        <f>AR3+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
+      <c r="AT4" s="8">
+        <f>AS4+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
         <v>33</v>
       </c>
-      <c r="AT3" s="8">
-        <f>AS3+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
+      <c r="AU4" s="8">
+        <f>AT4+'성장 시스템'!$D$12+'성장 시스템'!$D$15</f>
         <v>35</v>
       </c>
-      <c r="AU3" s="8">
-        <f>G3</f>
+      <c r="AV4" s="8">
+        <f>H4</f>
         <v>6</v>
       </c>
-      <c r="AV3" s="8">
-        <f>AU3+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
+      <c r="AW4" s="8">
+        <f>AV4+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
         <v>7</v>
       </c>
-      <c r="AW3" s="8">
-        <f>AV3+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
+      <c r="AX4" s="8">
+        <f>AW4+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
         <v>8</v>
       </c>
-      <c r="AX3" s="8">
-        <f>AW3+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
+      <c r="AY4" s="8">
+        <f>AX4+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
         <v>9</v>
       </c>
-      <c r="AY3" s="8">
-        <f>AX3+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
+      <c r="AZ4" s="8">
+        <f>AY4+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
         <v>10</v>
       </c>
-      <c r="AZ3" s="8">
-        <f>AY3+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
+      <c r="BA4" s="8">
+        <f>AZ4+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
         <v>11</v>
       </c>
-      <c r="BA3" s="8">
-        <f>AZ3+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
+      <c r="BB4" s="8">
+        <f>BA4+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
         <v>12</v>
       </c>
-      <c r="BB3" s="8">
-        <f>BA3+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
+      <c r="BC4" s="8">
+        <f>BB4+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
         <v>13</v>
       </c>
-      <c r="BC3" s="8">
-        <f>BB3+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
+      <c r="BD4" s="8">
+        <f>BC4+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
         <v>14</v>
       </c>
-      <c r="BD3" s="8">
-        <f>BC3+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
+      <c r="BE4" s="8">
+        <f>BD4+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
         <v>15</v>
       </c>
-      <c r="BE3" s="8">
-        <f>BD3+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
+      <c r="BF4" s="8">
+        <f>BE4+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
         <v>16</v>
       </c>
-      <c r="BF3" s="8">
-        <f>BE3+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
+      <c r="BG4" s="8">
+        <f>BF4+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
         <v>17</v>
       </c>
-      <c r="BG3" s="8">
-        <f>BF3+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
+      <c r="BH4" s="8">
+        <f>BG4+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
         <v>18</v>
       </c>
-      <c r="BH3" s="8">
-        <f>BG3+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
+      <c r="BI4" s="8">
+        <f>BH4+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
         <v>19</v>
       </c>
-      <c r="BI3" s="8">
-        <f>BH3+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
+      <c r="BJ4" s="8">
+        <f>BI4+'성장 시스템'!$E$12+'성장 시스템'!$E$15</f>
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.6">
-      <c r="A4" s="8">
+    <row r="5" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8">
         <v>10002</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>840</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D5" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="E5" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="E4" s="8">
+      <c r="F5" s="8">
         <v>4</v>
       </c>
-      <c r="F4" s="8">
+      <c r="G5" s="8">
         <v>12</v>
       </c>
-      <c r="G4" s="8">
+      <c r="H5" s="8">
         <v>4</v>
       </c>
-      <c r="H4" s="33">
+      <c r="I5" s="33">
         <v>0.3</v>
       </c>
-      <c r="I4" s="33">
+      <c r="J5" s="33">
         <v>0.1</v>
       </c>
-      <c r="J4" s="33">
+      <c r="K5" s="33">
         <v>0.2</v>
       </c>
-      <c r="K4" s="8">
+      <c r="L5" s="8">
         <v>3</v>
       </c>
-      <c r="L4" s="32" t="s">
+      <c r="M5" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N5" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="N4" s="63">
+      <c r="O5" s="63">
         <f>'성장 시스템'!$C$12+'성장 시스템'!C16</f>
         <v>1</v>
       </c>
-      <c r="O4" s="63">
+      <c r="P5" s="63">
         <f>'성장 시스템'!$D$12+'성장 시스템'!D16</f>
         <v>3</v>
       </c>
-      <c r="P4" s="63">
+      <c r="Q5" s="63">
         <f>'성장 시스템'!$E$12+'성장 시스템'!E16</f>
         <v>1</v>
       </c>
-      <c r="Q4" s="8">
-        <f t="shared" ref="Q4:Q7" si="0">E4</f>
+      <c r="R5" s="8">
+        <f t="shared" ref="R5:R8" si="0">F5</f>
         <v>4</v>
       </c>
-      <c r="R4" s="8">
-        <f>Q4+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
+      <c r="S5" s="8">
+        <f>R5+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
         <v>5</v>
       </c>
-      <c r="S4" s="8">
-        <f>R4+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
+      <c r="T5" s="8">
+        <f>S5+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
         <v>6</v>
       </c>
-      <c r="T4" s="8">
-        <f>S4+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
+      <c r="U5" s="8">
+        <f>T5+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
         <v>7</v>
       </c>
-      <c r="U4" s="8">
-        <f>T4+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
+      <c r="V5" s="8">
+        <f>U5+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
         <v>8</v>
       </c>
-      <c r="V4" s="8">
-        <f>U4+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
+      <c r="W5" s="8">
+        <f>V5+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
         <v>9</v>
       </c>
-      <c r="W4" s="8">
-        <f>V4+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
+      <c r="X5" s="8">
+        <f>W5+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
         <v>10</v>
       </c>
-      <c r="X4" s="8">
-        <f>W4+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
+      <c r="Y5" s="8">
+        <f>X5+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
         <v>11</v>
       </c>
-      <c r="Y4" s="8">
-        <f>X4+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
+      <c r="Z5" s="8">
+        <f>Y5+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
         <v>12</v>
       </c>
-      <c r="Z4" s="8">
-        <f>Y4+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
+      <c r="AA5" s="8">
+        <f>Z5+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
         <v>13</v>
       </c>
-      <c r="AA4" s="8">
-        <f>Z4+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
+      <c r="AB5" s="8">
+        <f>AA5+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
         <v>14</v>
       </c>
-      <c r="AB4" s="8">
-        <f>AA4+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
+      <c r="AC5" s="8">
+        <f>AB5+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
         <v>15</v>
       </c>
-      <c r="AC4" s="8">
-        <f>AB4+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
+      <c r="AD5" s="8">
+        <f>AC5+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
         <v>16</v>
       </c>
-      <c r="AD4" s="8">
-        <f>AC4+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
+      <c r="AE5" s="8">
+        <f>AD5+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
         <v>17</v>
       </c>
-      <c r="AE4" s="8">
-        <f>AD4+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
+      <c r="AF5" s="8">
+        <f>AE5+'성장 시스템'!$C$12+'성장 시스템'!$C$16</f>
         <v>18</v>
       </c>
-      <c r="AF4" s="8">
-        <f t="shared" ref="AF4:AF7" si="1">F4</f>
+      <c r="AG5" s="8">
+        <f t="shared" ref="AG5:AG8" si="1">G5</f>
         <v>12</v>
       </c>
-      <c r="AG4" s="8">
-        <f>AF4+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
+      <c r="AH5" s="8">
+        <f>AG5+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
         <v>15</v>
       </c>
-      <c r="AH4" s="8">
-        <f>AG4+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
+      <c r="AI5" s="8">
+        <f>AH5+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
         <v>18</v>
       </c>
-      <c r="AI4" s="8">
-        <f>AH4+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
+      <c r="AJ5" s="8">
+        <f>AI5+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
         <v>21</v>
       </c>
-      <c r="AJ4" s="8">
-        <f>AI4+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
+      <c r="AK5" s="8">
+        <f>AJ5+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
         <v>24</v>
       </c>
-      <c r="AK4" s="8">
-        <f>AJ4+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
+      <c r="AL5" s="8">
+        <f>AK5+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
         <v>27</v>
       </c>
-      <c r="AL4" s="8">
-        <f>AK4+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
+      <c r="AM5" s="8">
+        <f>AL5+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
         <v>30</v>
       </c>
-      <c r="AM4" s="8">
-        <f>AL4+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
+      <c r="AN5" s="8">
+        <f>AM5+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
         <v>33</v>
       </c>
-      <c r="AN4" s="8">
-        <f>AM4+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
+      <c r="AO5" s="8">
+        <f>AN5+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
         <v>36</v>
       </c>
-      <c r="AO4" s="8">
-        <f>AN4+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
+      <c r="AP5" s="8">
+        <f>AO5+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
         <v>39</v>
       </c>
-      <c r="AP4" s="8">
-        <f>AO4+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
+      <c r="AQ5" s="8">
+        <f>AP5+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
         <v>42</v>
       </c>
-      <c r="AQ4" s="8">
-        <f>AP4+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
+      <c r="AR5" s="8">
+        <f>AQ5+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
         <v>45</v>
       </c>
-      <c r="AR4" s="8">
-        <f>AQ4+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
+      <c r="AS5" s="8">
+        <f>AR5+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
         <v>48</v>
       </c>
-      <c r="AS4" s="8">
-        <f>AR4+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
+      <c r="AT5" s="8">
+        <f>AS5+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
         <v>51</v>
       </c>
-      <c r="AT4" s="8">
-        <f>AS4+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
+      <c r="AU5" s="8">
+        <f>AT5+'성장 시스템'!$D$12+'성장 시스템'!$D$16</f>
         <v>54</v>
       </c>
-      <c r="AU4" s="8">
-        <f t="shared" ref="AU4:AU7" si="2">G4</f>
+      <c r="AV5" s="8">
+        <f t="shared" ref="AV5:AV8" si="2">H5</f>
         <v>4</v>
       </c>
-      <c r="AV4" s="8">
-        <f>AU4+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
+      <c r="AW5" s="8">
+        <f>AV5+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
         <v>5</v>
       </c>
-      <c r="AW4" s="8">
-        <f>AV4+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
+      <c r="AX5" s="8">
+        <f>AW5+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
         <v>6</v>
       </c>
-      <c r="AX4" s="8">
-        <f>AW4+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
+      <c r="AY5" s="8">
+        <f>AX5+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
         <v>7</v>
       </c>
-      <c r="AY4" s="8">
-        <f>AX4+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
+      <c r="AZ5" s="8">
+        <f>AY5+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
         <v>8</v>
       </c>
-      <c r="AZ4" s="8">
-        <f>AY4+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
+      <c r="BA5" s="8">
+        <f>AZ5+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
         <v>9</v>
       </c>
-      <c r="BA4" s="8">
-        <f>AZ4+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
+      <c r="BB5" s="8">
+        <f>BA5+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
         <v>10</v>
       </c>
-      <c r="BB4" s="8">
-        <f>BA4+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
+      <c r="BC5" s="8">
+        <f>BB5+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
         <v>11</v>
       </c>
-      <c r="BC4" s="8">
-        <f>BB4+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
+      <c r="BD5" s="8">
+        <f>BC5+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
         <v>12</v>
       </c>
-      <c r="BD4" s="8">
-        <f>BC4+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
+      <c r="BE5" s="8">
+        <f>BD5+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
         <v>13</v>
       </c>
-      <c r="BE4" s="8">
-        <f>BD4+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
+      <c r="BF5" s="8">
+        <f>BE5+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
         <v>14</v>
       </c>
-      <c r="BF4" s="8">
-        <f>BE4+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
+      <c r="BG5" s="8">
+        <f>BF5+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
         <v>15</v>
       </c>
-      <c r="BG4" s="8">
-        <f>BF4+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
+      <c r="BH5" s="8">
+        <f>BG5+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
         <v>16</v>
       </c>
-      <c r="BH4" s="8">
-        <f>BG4+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
+      <c r="BI5" s="8">
+        <f>BH5+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
         <v>17</v>
       </c>
-      <c r="BI4" s="8">
-        <f>BH4+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
+      <c r="BJ5" s="8">
+        <f>BI5+'성장 시스템'!$E$12+'성장 시스템'!$E$16</f>
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.6">
-      <c r="A5" s="8">
+    <row r="6" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8">
         <v>10003</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C6" s="8" t="s">
         <v>841</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D6" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="E6" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E5" s="8">
+      <c r="F6" s="8">
         <v>6</v>
       </c>
-      <c r="F5" s="8">
+      <c r="G6" s="8">
         <v>12</v>
       </c>
-      <c r="G5" s="8">
+      <c r="H6" s="8">
         <v>2</v>
       </c>
-      <c r="H5" s="33">
+      <c r="I6" s="33">
         <v>0.2</v>
       </c>
-      <c r="I5" s="33">
+      <c r="J6" s="33">
         <v>0.05</v>
       </c>
-      <c r="J5" s="33">
+      <c r="K6" s="33">
         <v>0.1</v>
       </c>
-      <c r="K5" s="8">
+      <c r="L6" s="8">
         <v>2</v>
       </c>
-      <c r="L5" s="32" t="s">
+      <c r="M6" s="32" t="s">
         <v>725</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="N6" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="N5" s="63">
+      <c r="O6" s="63">
         <f>'성장 시스템'!$C$12+'성장 시스템'!C17</f>
         <v>2</v>
       </c>
-      <c r="O5" s="63">
+      <c r="P6" s="63">
         <f>'성장 시스템'!$D$12+'성장 시스템'!D17</f>
         <v>2</v>
       </c>
-      <c r="P5" s="63">
+      <c r="Q6" s="63">
         <f>'성장 시스템'!$E$12+'성장 시스템'!E17</f>
         <v>1</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="R6" s="8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="R5" s="8">
-        <f>Q5+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
+      <c r="S6" s="8">
+        <f>R6+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
         <v>8</v>
       </c>
-      <c r="S5" s="8">
-        <f>R5+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
+      <c r="T6" s="8">
+        <f>S6+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
         <v>10</v>
       </c>
-      <c r="T5" s="8">
-        <f>S5+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
+      <c r="U6" s="8">
+        <f>T6+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
         <v>12</v>
       </c>
-      <c r="U5" s="8">
-        <f>T5+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
+      <c r="V6" s="8">
+        <f>U6+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
         <v>14</v>
       </c>
-      <c r="V5" s="8">
-        <f>U5+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
+      <c r="W6" s="8">
+        <f>V6+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
         <v>16</v>
       </c>
-      <c r="W5" s="8">
-        <f>V5+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
+      <c r="X6" s="8">
+        <f>W6+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
         <v>18</v>
       </c>
-      <c r="X5" s="8">
-        <f>W5+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
+      <c r="Y6" s="8">
+        <f>X6+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
         <v>20</v>
       </c>
-      <c r="Y5" s="8">
-        <f>X5+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
+      <c r="Z6" s="8">
+        <f>Y6+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
         <v>22</v>
       </c>
-      <c r="Z5" s="8">
-        <f>Y5+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
+      <c r="AA6" s="8">
+        <f>Z6+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
         <v>24</v>
       </c>
-      <c r="AA5" s="8">
-        <f>Z5+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
+      <c r="AB6" s="8">
+        <f>AA6+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
         <v>26</v>
       </c>
-      <c r="AB5" s="8">
-        <f>AA5+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
+      <c r="AC6" s="8">
+        <f>AB6+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
         <v>28</v>
       </c>
-      <c r="AC5" s="8">
-        <f>AB5+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
+      <c r="AD6" s="8">
+        <f>AC6+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
         <v>30</v>
       </c>
-      <c r="AD5" s="8">
-        <f>AC5+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
+      <c r="AE6" s="8">
+        <f>AD6+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
         <v>32</v>
       </c>
-      <c r="AE5" s="8">
-        <f>AD5+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
+      <c r="AF6" s="8">
+        <f>AE6+'성장 시스템'!$C$12+'성장 시스템'!$C$17</f>
         <v>34</v>
       </c>
-      <c r="AF5" s="8">
+      <c r="AG6" s="8">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="AG5" s="8">
-        <f>AF5+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
+      <c r="AH6" s="8">
+        <f>AG6+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
         <v>14</v>
       </c>
-      <c r="AH5" s="8">
-        <f>AG5+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
+      <c r="AI6" s="8">
+        <f>AH6+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
         <v>16</v>
       </c>
-      <c r="AI5" s="8">
-        <f>AH5+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
+      <c r="AJ6" s="8">
+        <f>AI6+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
         <v>18</v>
       </c>
-      <c r="AJ5" s="8">
-        <f>AI5+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
+      <c r="AK6" s="8">
+        <f>AJ6+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
         <v>20</v>
       </c>
-      <c r="AK5" s="8">
-        <f>AJ5+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
+      <c r="AL6" s="8">
+        <f>AK6+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
         <v>22</v>
       </c>
-      <c r="AL5" s="8">
-        <f>AK5+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
+      <c r="AM6" s="8">
+        <f>AL6+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
         <v>24</v>
       </c>
-      <c r="AM5" s="8">
-        <f>AL5+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
+      <c r="AN6" s="8">
+        <f>AM6+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
         <v>26</v>
       </c>
-      <c r="AN5" s="8">
-        <f>AM5+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
+      <c r="AO6" s="8">
+        <f>AN6+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
         <v>28</v>
       </c>
-      <c r="AO5" s="8">
-        <f>AN5+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
+      <c r="AP6" s="8">
+        <f>AO6+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
         <v>30</v>
       </c>
-      <c r="AP5" s="8">
-        <f>AO5+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
+      <c r="AQ6" s="8">
+        <f>AP6+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
         <v>32</v>
       </c>
-      <c r="AQ5" s="8">
-        <f>AP5+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
+      <c r="AR6" s="8">
+        <f>AQ6+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
         <v>34</v>
       </c>
-      <c r="AR5" s="8">
-        <f>AQ5+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
+      <c r="AS6" s="8">
+        <f>AR6+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
         <v>36</v>
       </c>
-      <c r="AS5" s="8">
-        <f>AR5+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
+      <c r="AT6" s="8">
+        <f>AS6+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
         <v>38</v>
       </c>
-      <c r="AT5" s="8">
-        <f>AS5+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
+      <c r="AU6" s="8">
+        <f>AT6+'성장 시스템'!$D$12+'성장 시스템'!$D$17</f>
         <v>40</v>
       </c>
-      <c r="AU5" s="8">
+      <c r="AV6" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AV5" s="8">
-        <f>AU5+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
+      <c r="AW6" s="8">
+        <f>AV6+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
         <v>3</v>
       </c>
-      <c r="AW5" s="8">
-        <f>AV5+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
+      <c r="AX6" s="8">
+        <f>AW6+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
         <v>4</v>
       </c>
-      <c r="AX5" s="8">
-        <f>AW5+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
+      <c r="AY6" s="8">
+        <f>AX6+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
         <v>5</v>
       </c>
-      <c r="AY5" s="8">
-        <f>AX5+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
+      <c r="AZ6" s="8">
+        <f>AY6+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
         <v>6</v>
       </c>
-      <c r="AZ5" s="8">
-        <f>AY5+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
+      <c r="BA6" s="8">
+        <f>AZ6+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
         <v>7</v>
       </c>
-      <c r="BA5" s="8">
-        <f>AZ5+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
+      <c r="BB6" s="8">
+        <f>BA6+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
         <v>8</v>
       </c>
-      <c r="BB5" s="8">
-        <f>BA5+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
+      <c r="BC6" s="8">
+        <f>BB6+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
         <v>9</v>
       </c>
-      <c r="BC5" s="8">
-        <f>BB5+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
+      <c r="BD6" s="8">
+        <f>BC6+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
         <v>10</v>
       </c>
-      <c r="BD5" s="8">
-        <f>BC5+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
+      <c r="BE6" s="8">
+        <f>BD6+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
         <v>11</v>
       </c>
-      <c r="BE5" s="8">
-        <f>BD5+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
+      <c r="BF6" s="8">
+        <f>BE6+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
         <v>12</v>
       </c>
-      <c r="BF5" s="8">
-        <f>BE5+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
+      <c r="BG6" s="8">
+        <f>BF6+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
         <v>13</v>
       </c>
-      <c r="BG5" s="8">
-        <f>BF5+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
+      <c r="BH6" s="8">
+        <f>BG6+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
         <v>14</v>
       </c>
-      <c r="BH5" s="8">
-        <f>BG5+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
+      <c r="BI6" s="8">
+        <f>BH6+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
         <v>15</v>
       </c>
-      <c r="BI5" s="8">
-        <f>BH5+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
+      <c r="BJ6" s="8">
+        <f>BI6+'성장 시스템'!$E$12+'성장 시스템'!$E$17</f>
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.6">
-      <c r="A6" s="8">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8">
         <v>10004</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>842</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="E7" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E6" s="8">
+      <c r="F7" s="8">
         <v>6</v>
       </c>
-      <c r="F6" s="8">
+      <c r="G7" s="8">
         <v>8</v>
       </c>
-      <c r="G6" s="8">
+      <c r="H7" s="8">
         <v>6</v>
       </c>
-      <c r="H6" s="33">
+      <c r="I7" s="33">
         <v>0.1</v>
       </c>
-      <c r="I6" s="33">
+      <c r="J7" s="33">
         <v>0.1</v>
       </c>
-      <c r="J6" s="33">
+      <c r="K7" s="33">
         <v>0.15</v>
       </c>
-      <c r="K6" s="8">
+      <c r="L7" s="8">
         <v>2</v>
       </c>
-      <c r="L6" s="32" t="s">
+      <c r="M7" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="N7" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N6" s="63">
+      <c r="O7" s="63">
         <f>'성장 시스템'!$C$12+'성장 시스템'!C18</f>
         <v>2</v>
       </c>
-      <c r="O6" s="63">
+      <c r="P7" s="63">
         <f>'성장 시스템'!$D$12+'성장 시스템'!D18</f>
         <v>1</v>
       </c>
-      <c r="P6" s="63">
+      <c r="Q7" s="63">
         <f>'성장 시스템'!$E$12+'성장 시스템'!E18</f>
         <v>2</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="R7" s="8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="R6" s="8">
-        <f>Q6+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
+      <c r="S7" s="8">
+        <f>R7+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
         <v>8</v>
       </c>
-      <c r="S6" s="8">
-        <f>R6+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
+      <c r="T7" s="8">
+        <f>S7+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
         <v>10</v>
       </c>
-      <c r="T6" s="8">
-        <f>S6+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
+      <c r="U7" s="8">
+        <f>T7+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
         <v>12</v>
       </c>
-      <c r="U6" s="8">
-        <f>T6+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
+      <c r="V7" s="8">
+        <f>U7+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
         <v>14</v>
       </c>
-      <c r="V6" s="8">
-        <f>U6+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
+      <c r="W7" s="8">
+        <f>V7+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
         <v>16</v>
       </c>
-      <c r="W6" s="8">
-        <f>V6+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
+      <c r="X7" s="8">
+        <f>W7+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
         <v>18</v>
       </c>
-      <c r="X6" s="8">
-        <f>W6+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
+      <c r="Y7" s="8">
+        <f>X7+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
         <v>20</v>
       </c>
-      <c r="Y6" s="8">
-        <f>X6+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
+      <c r="Z7" s="8">
+        <f>Y7+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
         <v>22</v>
       </c>
-      <c r="Z6" s="8">
-        <f>Y6+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
+      <c r="AA7" s="8">
+        <f>Z7+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
         <v>24</v>
       </c>
-      <c r="AA6" s="8">
-        <f>Z6+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
+      <c r="AB7" s="8">
+        <f>AA7+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
         <v>26</v>
       </c>
-      <c r="AB6" s="8">
-        <f>AA6+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
+      <c r="AC7" s="8">
+        <f>AB7+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
         <v>28</v>
       </c>
-      <c r="AC6" s="8">
-        <f>AB6+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
+      <c r="AD7" s="8">
+        <f>AC7+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
         <v>30</v>
       </c>
-      <c r="AD6" s="8">
-        <f>AC6+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
+      <c r="AE7" s="8">
+        <f>AD7+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
         <v>32</v>
       </c>
-      <c r="AE6" s="8">
-        <f>AD6+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
+      <c r="AF7" s="8">
+        <f>AE7+'성장 시스템'!$C$12+'성장 시스템'!$C$18</f>
         <v>34</v>
       </c>
-      <c r="AF6" s="8">
+      <c r="AG7" s="8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="AG6" s="8">
-        <f>AF6+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
+      <c r="AH7" s="8">
+        <f>AG7+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
         <v>9</v>
       </c>
-      <c r="AH6" s="8">
-        <f>AG6+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
+      <c r="AI7" s="8">
+        <f>AH7+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
         <v>10</v>
       </c>
-      <c r="AI6" s="8">
-        <f>AH6+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
+      <c r="AJ7" s="8">
+        <f>AI7+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
         <v>11</v>
       </c>
-      <c r="AJ6" s="8">
-        <f>AI6+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
+      <c r="AK7" s="8">
+        <f>AJ7+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
         <v>12</v>
       </c>
-      <c r="AK6" s="8">
-        <f>AJ6+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
+      <c r="AL7" s="8">
+        <f>AK7+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
         <v>13</v>
       </c>
-      <c r="AL6" s="8">
-        <f>AK6+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
+      <c r="AM7" s="8">
+        <f>AL7+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
         <v>14</v>
       </c>
-      <c r="AM6" s="8">
-        <f>AL6+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
+      <c r="AN7" s="8">
+        <f>AM7+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
         <v>15</v>
       </c>
-      <c r="AN6" s="8">
-        <f>AM6+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
+      <c r="AO7" s="8">
+        <f>AN7+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
         <v>16</v>
       </c>
-      <c r="AO6" s="8">
-        <f>AN6+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
+      <c r="AP7" s="8">
+        <f>AO7+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
         <v>17</v>
       </c>
-      <c r="AP6" s="8">
-        <f>AO6+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
+      <c r="AQ7" s="8">
+        <f>AP7+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
         <v>18</v>
       </c>
-      <c r="AQ6" s="8">
-        <f>AP6+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
+      <c r="AR7" s="8">
+        <f>AQ7+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
         <v>19</v>
       </c>
-      <c r="AR6" s="8">
-        <f>AQ6+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
+      <c r="AS7" s="8">
+        <f>AR7+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
         <v>20</v>
       </c>
-      <c r="AS6" s="8">
-        <f>AR6+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
+      <c r="AT7" s="8">
+        <f>AS7+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
         <v>21</v>
       </c>
-      <c r="AT6" s="8">
-        <f>AS6+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
+      <c r="AU7" s="8">
+        <f>AT7+'성장 시스템'!$D$12+'성장 시스템'!$D$18</f>
         <v>22</v>
       </c>
-      <c r="AU6" s="8">
+      <c r="AV7" s="8">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="AV6" s="8">
-        <f>AU6+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
+      <c r="AW7" s="8">
+        <f>AV7+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
         <v>8</v>
       </c>
-      <c r="AW6" s="8">
-        <f>AV6+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
+      <c r="AX7" s="8">
+        <f>AW7+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
         <v>10</v>
       </c>
-      <c r="AX6" s="8">
-        <f>AW6+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
+      <c r="AY7" s="8">
+        <f>AX7+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
         <v>12</v>
       </c>
-      <c r="AY6" s="8">
-        <f>AX6+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
+      <c r="AZ7" s="8">
+        <f>AY7+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
         <v>14</v>
       </c>
-      <c r="AZ6" s="8">
-        <f>AY6+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
+      <c r="BA7" s="8">
+        <f>AZ7+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
         <v>16</v>
       </c>
-      <c r="BA6" s="8">
-        <f>AZ6+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
+      <c r="BB7" s="8">
+        <f>BA7+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
         <v>18</v>
       </c>
-      <c r="BB6" s="8">
-        <f>BA6+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
+      <c r="BC7" s="8">
+        <f>BB7+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
         <v>20</v>
       </c>
-      <c r="BC6" s="8">
-        <f>BB6+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
+      <c r="BD7" s="8">
+        <f>BC7+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
         <v>22</v>
       </c>
-      <c r="BD6" s="8">
-        <f>BC6+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
+      <c r="BE7" s="8">
+        <f>BD7+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
         <v>24</v>
       </c>
-      <c r="BE6" s="8">
-        <f>BD6+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
+      <c r="BF7" s="8">
+        <f>BE7+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
         <v>26</v>
       </c>
-      <c r="BF6" s="8">
-        <f>BE6+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
+      <c r="BG7" s="8">
+        <f>BF7+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
         <v>28</v>
       </c>
-      <c r="BG6" s="8">
-        <f>BF6+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
+      <c r="BH7" s="8">
+        <f>BG7+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
         <v>30</v>
       </c>
-      <c r="BH6" s="8">
-        <f>BG6+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
+      <c r="BI7" s="8">
+        <f>BH7+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
         <v>32</v>
       </c>
-      <c r="BI6" s="8">
-        <f>BH6+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
+      <c r="BJ7" s="8">
+        <f>BI7+'성장 시스템'!$E$12+'성장 시스템'!$E$18</f>
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.6">
-      <c r="A7" s="8">
+    <row r="8" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8">
         <v>10005</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>843</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>554</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="E8" s="21" t="s">
         <v>364</v>
       </c>
-      <c r="E7" s="8">
+      <c r="F8" s="8">
         <v>6</v>
       </c>
-      <c r="F7" s="8">
+      <c r="G8" s="8">
         <v>9</v>
       </c>
-      <c r="G7" s="8">
+      <c r="H8" s="8">
         <v>5</v>
       </c>
-      <c r="H7" s="33">
+      <c r="I8" s="33">
         <v>0.15</v>
       </c>
-      <c r="I7" s="33">
+      <c r="J8" s="33">
         <v>0.15</v>
       </c>
-      <c r="J7" s="33">
+      <c r="K8" s="33">
         <v>0.15</v>
       </c>
-      <c r="K7" s="8">
+      <c r="L8" s="8">
         <v>2</v>
       </c>
-      <c r="L7" s="32" t="s">
+      <c r="M8" s="32" t="s">
         <v>365</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="N8" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="N7" s="63">
+      <c r="O8" s="63">
         <f>'성장 시스템'!$C$12+'성장 시스템'!C19</f>
         <v>1</v>
       </c>
-      <c r="O7" s="63">
+      <c r="P8" s="63">
         <f>'성장 시스템'!$D$12+'성장 시스템'!D19</f>
         <v>2</v>
       </c>
-      <c r="P7" s="63">
+      <c r="Q8" s="63">
         <f>'성장 시스템'!$E$12+'성장 시스템'!E19</f>
         <v>2</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="R8" s="8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="R7" s="8">
-        <f>Q7+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
+      <c r="S8" s="8">
+        <f>R8+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
         <v>7</v>
       </c>
-      <c r="S7" s="8">
-        <f>R7+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
+      <c r="T8" s="8">
+        <f>S8+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
         <v>8</v>
       </c>
-      <c r="T7" s="8">
-        <f>S7+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
+      <c r="U8" s="8">
+        <f>T8+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
         <v>9</v>
       </c>
-      <c r="U7" s="8">
-        <f>T7+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
+      <c r="V8" s="8">
+        <f>U8+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
         <v>10</v>
       </c>
-      <c r="V7" s="8">
-        <f>U7+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
+      <c r="W8" s="8">
+        <f>V8+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
         <v>11</v>
       </c>
-      <c r="W7" s="8">
-        <f>V7+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
+      <c r="X8" s="8">
+        <f>W8+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
         <v>12</v>
       </c>
-      <c r="X7" s="8">
-        <f>W7+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
+      <c r="Y8" s="8">
+        <f>X8+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
         <v>13</v>
       </c>
-      <c r="Y7" s="8">
-        <f>X7+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
+      <c r="Z8" s="8">
+        <f>Y8+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
         <v>14</v>
       </c>
-      <c r="Z7" s="8">
-        <f>Y7+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
+      <c r="AA8" s="8">
+        <f>Z8+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
         <v>15</v>
       </c>
-      <c r="AA7" s="8">
-        <f>Z7+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
+      <c r="AB8" s="8">
+        <f>AA8+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
         <v>16</v>
       </c>
-      <c r="AB7" s="8">
-        <f>AA7+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
+      <c r="AC8" s="8">
+        <f>AB8+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
         <v>17</v>
       </c>
-      <c r="AC7" s="8">
-        <f>AB7+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
+      <c r="AD8" s="8">
+        <f>AC8+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
         <v>18</v>
       </c>
-      <c r="AD7" s="8">
-        <f>AC7+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
+      <c r="AE8" s="8">
+        <f>AD8+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
         <v>19</v>
       </c>
-      <c r="AE7" s="8">
-        <f>AD7+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
+      <c r="AF8" s="8">
+        <f>AE8+'성장 시스템'!$C$12+'성장 시스템'!$C$19</f>
         <v>20</v>
       </c>
-      <c r="AF7" s="8">
+      <c r="AG8" s="8">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="AG7" s="8">
-        <f>AF7+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
+      <c r="AH8" s="8">
+        <f>AG8+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
         <v>11</v>
       </c>
-      <c r="AH7" s="8">
-        <f>AG7+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
+      <c r="AI8" s="8">
+        <f>AH8+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
         <v>13</v>
       </c>
-      <c r="AI7" s="8">
-        <f>AH7+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
+      <c r="AJ8" s="8">
+        <f>AI8+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
         <v>15</v>
       </c>
-      <c r="AJ7" s="8">
-        <f>AI7+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
+      <c r="AK8" s="8">
+        <f>AJ8+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
         <v>17</v>
       </c>
-      <c r="AK7" s="8">
-        <f>AJ7+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
+      <c r="AL8" s="8">
+        <f>AK8+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
         <v>19</v>
       </c>
-      <c r="AL7" s="8">
-        <f>AK7+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
+      <c r="AM8" s="8">
+        <f>AL8+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
         <v>21</v>
       </c>
-      <c r="AM7" s="8">
-        <f>AL7+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
+      <c r="AN8" s="8">
+        <f>AM8+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
         <v>23</v>
       </c>
-      <c r="AN7" s="8">
-        <f>AM7+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
+      <c r="AO8" s="8">
+        <f>AN8+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
         <v>25</v>
       </c>
-      <c r="AO7" s="8">
-        <f>AN7+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
+      <c r="AP8" s="8">
+        <f>AO8+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
         <v>27</v>
       </c>
-      <c r="AP7" s="8">
-        <f>AO7+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
+      <c r="AQ8" s="8">
+        <f>AP8+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
         <v>29</v>
       </c>
-      <c r="AQ7" s="8">
-        <f>AP7+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
+      <c r="AR8" s="8">
+        <f>AQ8+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
         <v>31</v>
       </c>
-      <c r="AR7" s="8">
-        <f>AQ7+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
+      <c r="AS8" s="8">
+        <f>AR8+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
         <v>33</v>
       </c>
-      <c r="AS7" s="8">
-        <f>AR7+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
+      <c r="AT8" s="8">
+        <f>AS8+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
         <v>35</v>
       </c>
-      <c r="AT7" s="8">
-        <f>AS7+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
+      <c r="AU8" s="8">
+        <f>AT8+'성장 시스템'!$D$12+'성장 시스템'!$D$19</f>
         <v>37</v>
       </c>
-      <c r="AU7" s="8">
+      <c r="AV8" s="8">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="AV7" s="8">
-        <f>AU7+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
+      <c r="AW8" s="8">
+        <f>AV8+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
         <v>7</v>
       </c>
-      <c r="AW7" s="8">
-        <f>AV7+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
+      <c r="AX8" s="8">
+        <f>AW8+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
         <v>9</v>
       </c>
-      <c r="AX7" s="8">
-        <f>AW7+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
+      <c r="AY8" s="8">
+        <f>AX8+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
         <v>11</v>
       </c>
-      <c r="AY7" s="8">
-        <f>AX7+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
+      <c r="AZ8" s="8">
+        <f>AY8+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
         <v>13</v>
       </c>
-      <c r="AZ7" s="8">
-        <f>AY7+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
+      <c r="BA8" s="8">
+        <f>AZ8+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
         <v>15</v>
       </c>
-      <c r="BA7" s="8">
-        <f>AZ7+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
+      <c r="BB8" s="8">
+        <f>BA8+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
         <v>17</v>
       </c>
-      <c r="BB7" s="8">
-        <f>BA7+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
+      <c r="BC8" s="8">
+        <f>BB8+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
         <v>19</v>
       </c>
-      <c r="BC7" s="8">
-        <f>BB7+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
+      <c r="BD8" s="8">
+        <f>BC8+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
         <v>21</v>
       </c>
-      <c r="BD7" s="8">
-        <f>BC7+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
+      <c r="BE8" s="8">
+        <f>BD8+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
         <v>23</v>
       </c>
-      <c r="BE7" s="8">
-        <f>BD7+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
+      <c r="BF8" s="8">
+        <f>BE8+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
         <v>25</v>
       </c>
-      <c r="BF7" s="8">
-        <f>BE7+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
+      <c r="BG8" s="8">
+        <f>BF8+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
         <v>27</v>
       </c>
-      <c r="BG7" s="8">
-        <f>BF7+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
+      <c r="BH8" s="8">
+        <f>BG8+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
         <v>29</v>
       </c>
-      <c r="BH7" s="8">
-        <f>BG7+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
+      <c r="BI8" s="8">
+        <f>BH8+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
         <v>31</v>
       </c>
-      <c r="BI7" s="8">
-        <f>BH7+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
+      <c r="BJ8" s="8">
+        <f>BI8+'성장 시스템'!$E$12+'성장 시스템'!$E$19</f>
         <v>33</v>
       </c>
+    </row>
+    <row r="9" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="10" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A10" s="8"/>
+    </row>
+    <row r="11" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A11" s="8"/>
+    </row>
+    <row r="12" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A12" s="8"/>
+    </row>
+    <row r="13" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A13" s="8"/>
+    </row>
+    <row r="14" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A14" s="8"/>
+    </row>
+    <row r="15" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A15" s="8"/>
+    </row>
+    <row r="16" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A16" s="8"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A17" s="8"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A18" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -14583,34 +14723,34 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AABADE7-A9EA-4249-8EFA-07CD80AB79A9}">
   <dimension ref="A1:AI34"/>
-  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.5625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="20.5625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.58203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="20.58203125" style="8" customWidth="1"/>
     <col min="3" max="3" width="15.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="16.5625" style="8" customWidth="1"/>
-    <col min="7" max="9" width="12.5625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="12.5625" style="39" customWidth="1"/>
-    <col min="11" max="11" width="20.5625" style="35" customWidth="1"/>
+    <col min="4" max="6" width="16.58203125" style="8" customWidth="1"/>
+    <col min="7" max="9" width="12.58203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="12.58203125" style="39" customWidth="1"/>
+    <col min="11" max="11" width="20.58203125" style="35" customWidth="1"/>
     <col min="12" max="12" width="38.25" style="35" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.5625" style="18" customWidth="1"/>
-    <col min="14" max="16" width="20.5625" style="8" customWidth="1"/>
-    <col min="17" max="19" width="20.5625" style="57" customWidth="1"/>
-    <col min="20" max="20" width="20.5625" style="39" customWidth="1"/>
-    <col min="21" max="21" width="20.5625" style="35" customWidth="1"/>
-    <col min="22" max="22" width="30.5625" style="35" customWidth="1"/>
-    <col min="23" max="23" width="20.5625" style="18" customWidth="1"/>
-    <col min="24" max="26" width="20.5625" style="8" customWidth="1"/>
-    <col min="27" max="29" width="20.5625" style="57" customWidth="1"/>
-    <col min="30" max="30" width="20.5625" style="39" customWidth="1"/>
+    <col min="13" max="13" width="20.58203125" style="18" customWidth="1"/>
+    <col min="14" max="16" width="20.58203125" style="8" customWidth="1"/>
+    <col min="17" max="19" width="20.58203125" style="57" customWidth="1"/>
+    <col min="20" max="20" width="20.58203125" style="39" customWidth="1"/>
+    <col min="21" max="21" width="20.58203125" style="35" customWidth="1"/>
+    <col min="22" max="22" width="30.58203125" style="35" customWidth="1"/>
+    <col min="23" max="23" width="20.58203125" style="18" customWidth="1"/>
+    <col min="24" max="26" width="20.58203125" style="8" customWidth="1"/>
+    <col min="27" max="29" width="20.58203125" style="57" customWidth="1"/>
+    <col min="30" max="30" width="20.58203125" style="39" customWidth="1"/>
     <col min="31" max="31" width="73" style="56" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20.5625" style="35" customWidth="1"/>
-    <col min="33" max="33" width="28.8125" style="127" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="20.5625" style="127" customWidth="1"/>
-    <col min="36" max="16384" width="8.5625" style="16"/>
+    <col min="32" max="32" width="20.58203125" style="35" customWidth="1"/>
+    <col min="33" max="33" width="28.83203125" style="127" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="20.58203125" style="127" customWidth="1"/>
+    <col min="36" max="16384" width="8.58203125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:35" ht="34" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>107</v>
       </c>
@@ -14717,7 +14857,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="101.25" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:35" ht="102" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>151</v>
       </c>
@@ -14824,7 +14964,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A3" s="8">
         <v>20001</v>
       </c>
@@ -14919,7 +15059,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A4" s="8">
         <v>20002</v>
       </c>
@@ -15002,7 +15142,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A5" s="8">
         <v>20003</v>
       </c>
@@ -15091,7 +15231,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
       <c r="N8" s="18"/>
@@ -15110,7 +15250,7 @@
       <c r="AB8" s="58"/>
       <c r="AC8" s="58"/>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
       <c r="N9" s="18"/>
@@ -15125,7 +15265,7 @@
       <c r="X9" s="18"/>
       <c r="Y9" s="18"/>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
       <c r="N10" s="18"/>
@@ -15144,7 +15284,7 @@
       <c r="AB10" s="58"/>
       <c r="AC10" s="58"/>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.45">
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="N11" s="18"/>
@@ -15163,7 +15303,7 @@
       <c r="AB11" s="58"/>
       <c r="AC11" s="58"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.45">
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="N12" s="18"/>
@@ -15182,7 +15322,7 @@
       <c r="AB12" s="58"/>
       <c r="AC12" s="58"/>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.45">
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="N13" s="18"/>
@@ -15201,7 +15341,7 @@
       <c r="AB13" s="58"/>
       <c r="AC13" s="58"/>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.45">
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
       <c r="N14" s="18"/>
@@ -15220,7 +15360,7 @@
       <c r="AB14" s="58"/>
       <c r="AC14" s="58"/>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.45">
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="N15" s="18"/>
@@ -15239,7 +15379,7 @@
       <c r="AB15" s="58"/>
       <c r="AC15" s="58"/>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.45">
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
       <c r="N16" s="18"/>
@@ -15258,7 +15398,7 @@
       <c r="AB16" s="58"/>
       <c r="AC16" s="58"/>
     </row>
-    <row r="17" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="17" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="N17" s="18"/>
@@ -15277,7 +15417,7 @@
       <c r="AB17" s="58"/>
       <c r="AC17" s="58"/>
     </row>
-    <row r="18" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="18" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="N18" s="18"/>
@@ -15296,7 +15436,7 @@
       <c r="AB18" s="58"/>
       <c r="AC18" s="58"/>
     </row>
-    <row r="19" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="19" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
       <c r="N19" s="18"/>
@@ -15315,7 +15455,7 @@
       <c r="AB19" s="58"/>
       <c r="AC19" s="58"/>
     </row>
-    <row r="20" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="20" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
       <c r="N20" s="18"/>
@@ -15334,7 +15474,7 @@
       <c r="AB20" s="58"/>
       <c r="AC20" s="58"/>
     </row>
-    <row r="21" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="21" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
       <c r="N21" s="18"/>
@@ -15353,7 +15493,7 @@
       <c r="AB21" s="58"/>
       <c r="AC21" s="58"/>
     </row>
-    <row r="22" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="22" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
       <c r="N22" s="18"/>
@@ -15372,7 +15512,7 @@
       <c r="AB22" s="58"/>
       <c r="AC22" s="58"/>
     </row>
-    <row r="23" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="23" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
       <c r="N23" s="18"/>
@@ -15391,7 +15531,7 @@
       <c r="AB23" s="58"/>
       <c r="AC23" s="58"/>
     </row>
-    <row r="24" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="24" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
       <c r="N24" s="18"/>
@@ -15410,7 +15550,7 @@
       <c r="AB24" s="58"/>
       <c r="AC24" s="58"/>
     </row>
-    <row r="25" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="25" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
       <c r="N25" s="18"/>
@@ -15429,7 +15569,7 @@
       <c r="AB25" s="58"/>
       <c r="AC25" s="58"/>
     </row>
-    <row r="26" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="26" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
       <c r="N26" s="18"/>
@@ -15448,7 +15588,7 @@
       <c r="AB26" s="58"/>
       <c r="AC26" s="58"/>
     </row>
-    <row r="27" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="27" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
       <c r="N27" s="18"/>
@@ -15467,7 +15607,7 @@
       <c r="AB27" s="58"/>
       <c r="AC27" s="58"/>
     </row>
-    <row r="28" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="28" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
       <c r="N28" s="18"/>
@@ -15486,7 +15626,7 @@
       <c r="AB28" s="58"/>
       <c r="AC28" s="58"/>
     </row>
-    <row r="29" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="29" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
       <c r="N29" s="18"/>
@@ -15505,7 +15645,7 @@
       <c r="AB29" s="58"/>
       <c r="AC29" s="58"/>
     </row>
-    <row r="30" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="30" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
       <c r="N30" s="18"/>
@@ -15524,7 +15664,7 @@
       <c r="AB30" s="58"/>
       <c r="AC30" s="58"/>
     </row>
-    <row r="31" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="31" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
       <c r="N31" s="18"/>
@@ -15543,7 +15683,7 @@
       <c r="AB31" s="58"/>
       <c r="AC31" s="58"/>
     </row>
-    <row r="32" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="32" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
       <c r="N32" s="18"/>
@@ -15562,7 +15702,7 @@
       <c r="AB32" s="58"/>
       <c r="AC32" s="58"/>
     </row>
-    <row r="33" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="33" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
       <c r="N33" s="18"/>
@@ -15581,7 +15721,7 @@
       <c r="AB33" s="58"/>
       <c r="AC33" s="58"/>
     </row>
-    <row r="34" spans="11:29" x14ac:dyDescent="0.6">
+    <row r="34" spans="11:29" x14ac:dyDescent="0.45">
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
       <c r="N34" s="18"/>
@@ -15609,16 +15749,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA6C9-D1CB-4A52-BF28-A60DE79D71F3}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="12.5625" defaultRowHeight="17.649999999999999" thickTop="1" thickBottom="1" x14ac:dyDescent="0.65"/>
+  <sheetFormatPr defaultColWidth="12.58203125" defaultRowHeight="18" thickTop="1" thickBottom="1" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="5" width="12.5625" style="1"/>
-    <col min="6" max="8" width="20.5625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="20.5625" style="68" hidden="1" customWidth="1"/>
-    <col min="11" max="12" width="20.5625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="12.5625" style="1"/>
+    <col min="1" max="5" width="12.58203125" style="1"/>
+    <col min="6" max="8" width="20.58203125" style="1" customWidth="1"/>
+    <col min="9" max="10" width="20.58203125" style="68" hidden="1" customWidth="1"/>
+    <col min="11" max="12" width="20.58203125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="12.58203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="34.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:12" ht="35" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="93" t="s">
         <v>380</v>
       </c>
@@ -15656,7 +15796,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="51.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:12" ht="52" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="93" t="s">
         <v>547</v>
       </c>
@@ -15694,7 +15834,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="3" spans="1:12" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:12" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="8">
         <v>30001</v>
       </c>
@@ -15730,7 +15870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:12" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="8">
         <v>30002</v>
       </c>
@@ -15766,7 +15906,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="5" spans="1:12" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="8">
         <v>30003</v>
       </c>
@@ -15811,17 +15951,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86EFE46D-4BB7-427B-9F0B-E6CCD845ECB0}">
   <dimension ref="A1:Y37"/>
-  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="4" width="20.5625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="73.1875" style="9" customWidth="1"/>
-    <col min="6" max="7" width="20.5625" style="18" customWidth="1"/>
-    <col min="8" max="13" width="20.5625" style="8" customWidth="1"/>
-    <col min="14" max="21" width="25.5625" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="8.5625" style="1"/>
+    <col min="1" max="4" width="20.58203125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="73.1640625" style="9" customWidth="1"/>
+    <col min="6" max="7" width="20.58203125" style="18" customWidth="1"/>
+    <col min="8" max="13" width="20.58203125" style="8" customWidth="1"/>
+    <col min="14" max="21" width="25.58203125" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="8.58203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:25" ht="34" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>42</v>
       </c>
@@ -15886,7 +16026,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="101.25" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:25" ht="102" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>43</v>
       </c>
@@ -15950,13 +16090,13 @@
       <c r="U2" s="129" t="s">
         <v>802</v>
       </c>
-      <c r="W2" s="138" t="s">
+      <c r="W2" s="144" t="s">
         <v>295</v>
       </c>
-      <c r="X2" s="138"/>
-      <c r="Y2" s="138"/>
-    </row>
-    <row r="3" spans="1:25" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="X2" s="144"/>
+      <c r="Y2" s="144"/>
+    </row>
+    <row r="3" spans="1:25" ht="34" x14ac:dyDescent="0.45">
       <c r="A3" s="8">
         <v>1010</v>
       </c>
@@ -16025,7 +16165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A4" s="8">
         <v>1020</v>
       </c>
@@ -16100,7 +16240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="50.65" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:25" ht="51" x14ac:dyDescent="0.45">
       <c r="A5" s="8">
         <v>1030</v>
       </c>
@@ -16180,7 +16320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:25" ht="34" x14ac:dyDescent="0.45">
       <c r="A6" s="8">
         <v>1040</v>
       </c>
@@ -16252,7 +16392,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A7" s="8">
         <v>1050</v>
       </c>
@@ -16312,7 +16452,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A8" s="8">
         <v>1060</v>
       </c>
@@ -16372,7 +16512,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:25" ht="34" x14ac:dyDescent="0.45">
       <c r="A9" s="8">
         <v>1070</v>
       </c>
@@ -16429,7 +16569,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A10" s="10">
         <v>2010</v>
       </c>
@@ -16463,36 +16603,36 @@
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
-      <c r="N10" s="144">
+      <c r="N10" s="132">
         <v>1</v>
       </c>
-      <c r="O10" s="144"/>
-      <c r="P10" s="144">
+      <c r="O10" s="132"/>
+      <c r="P10" s="132">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
-      <c r="Q10" s="144" t="str">
+      <c r="Q10" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R10" s="144">
+      <c r="R10" s="132">
         <f t="shared" si="3"/>
         <v>1.4</v>
       </c>
-      <c r="S10" s="144" t="str">
+      <c r="S10" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T10" s="144">
+      <c r="T10" s="132">
         <f t="shared" si="5"/>
         <v>1.7</v>
       </c>
-      <c r="U10" s="144" t="str">
+      <c r="U10" s="132" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A11" s="10">
         <v>2020</v>
       </c>
@@ -16530,36 +16670,36 @@
         <v>0</v>
       </c>
       <c r="M11" s="10"/>
-      <c r="N11" s="144">
+      <c r="N11" s="132">
         <v>0.6</v>
       </c>
-      <c r="O11" s="144"/>
-      <c r="P11" s="144">
+      <c r="O11" s="132"/>
+      <c r="P11" s="132">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="Q11" s="144" t="str">
+      <c r="Q11" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R11" s="144">
+      <c r="R11" s="132">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="S11" s="144" t="str">
+      <c r="S11" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T11" s="144">
+      <c r="T11" s="132">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="U11" s="144" t="str">
+      <c r="U11" s="132" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A12" s="10">
         <v>2030</v>
       </c>
@@ -16593,36 +16733,36 @@
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
-      <c r="N12" s="144">
+      <c r="N12" s="132">
         <v>1.8</v>
       </c>
-      <c r="O12" s="144"/>
-      <c r="P12" s="144">
+      <c r="O12" s="132"/>
+      <c r="P12" s="132">
         <f t="shared" si="1"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="Q12" s="144" t="str">
+      <c r="Q12" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R12" s="144">
+      <c r="R12" s="132">
         <f t="shared" si="3"/>
         <v>2.6</v>
       </c>
-      <c r="S12" s="144" t="str">
+      <c r="S12" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T12" s="144">
+      <c r="T12" s="132">
         <f t="shared" si="5"/>
         <v>3.1</v>
       </c>
-      <c r="U12" s="144" t="str">
+      <c r="U12" s="132" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:25" ht="34" x14ac:dyDescent="0.45">
       <c r="A13" s="10">
         <v>2040</v>
       </c>
@@ -16662,38 +16802,38 @@
       <c r="M13" s="10">
         <v>1</v>
       </c>
-      <c r="N13" s="144">
+      <c r="N13" s="132">
         <v>0.6</v>
       </c>
-      <c r="O13" s="144">
+      <c r="O13" s="132">
         <v>0.5</v>
       </c>
-      <c r="P13" s="144">
+      <c r="P13" s="132">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="Q13" s="144">
+      <c r="Q13" s="132">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
-      <c r="R13" s="144">
+      <c r="R13" s="132">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="S13" s="144">
+      <c r="S13" s="132">
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="T13" s="144">
+      <c r="T13" s="132">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="U13" s="144">
+      <c r="U13" s="132">
         <f t="shared" si="6"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A14" s="10">
         <v>2050</v>
       </c>
@@ -16727,36 +16867,36 @@
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
-      <c r="N14" s="144">
+      <c r="N14" s="132">
         <v>0.8</v>
       </c>
-      <c r="O14" s="144"/>
-      <c r="P14" s="144">
+      <c r="O14" s="132"/>
+      <c r="P14" s="132">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q14" s="144" t="str">
+      <c r="Q14" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R14" s="144">
+      <c r="R14" s="132">
         <f t="shared" si="3"/>
         <v>1.2</v>
       </c>
-      <c r="S14" s="144" t="str">
+      <c r="S14" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T14" s="144">
+      <c r="T14" s="132">
         <f t="shared" si="5"/>
         <v>1.4</v>
       </c>
-      <c r="U14" s="144" t="str">
+      <c r="U14" s="132" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:25" ht="34" x14ac:dyDescent="0.45">
       <c r="A15" s="10">
         <v>2060</v>
       </c>
@@ -16790,36 +16930,36 @@
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
       <c r="M15" s="10"/>
-      <c r="N15" s="144">
+      <c r="N15" s="132">
         <v>1.5</v>
       </c>
-      <c r="O15" s="144"/>
-      <c r="P15" s="144">
+      <c r="O15" s="132"/>
+      <c r="P15" s="132">
         <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
-      <c r="Q15" s="144" t="str">
+      <c r="Q15" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R15" s="144">
+      <c r="R15" s="132">
         <f t="shared" si="3"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="S15" s="144" t="str">
+      <c r="S15" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T15" s="144">
+      <c r="T15" s="132">
         <f t="shared" si="5"/>
         <v>2.6</v>
       </c>
-      <c r="U15" s="144" t="str">
+      <c r="U15" s="132" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:25" ht="34" x14ac:dyDescent="0.45">
       <c r="A16" s="10">
         <v>2070</v>
       </c>
@@ -16853,33 +16993,33 @@
       <c r="K16" s="10"/>
       <c r="L16" s="10"/>
       <c r="M16" s="10"/>
-      <c r="N16" s="144">
+      <c r="N16" s="132">
         <v>1.4</v>
       </c>
-      <c r="O16" s="144"/>
-      <c r="P16" s="144">
+      <c r="O16" s="132"/>
+      <c r="P16" s="132">
         <v>1.6</v>
       </c>
-      <c r="Q16" s="144" t="str">
+      <c r="Q16" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R16" s="144">
+      <c r="R16" s="132">
         <v>1.8</v>
       </c>
-      <c r="S16" s="144" t="str">
+      <c r="S16" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T16" s="144">
+      <c r="T16" s="132">
         <v>2</v>
       </c>
-      <c r="U16" s="144" t="str">
+      <c r="U16" s="132" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A17" s="8">
         <v>3010</v>
       </c>
@@ -16939,7 +17079,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:21" ht="34" x14ac:dyDescent="0.45">
       <c r="A18" s="8">
         <v>3020</v>
       </c>
@@ -16999,7 +17139,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:21" ht="34" x14ac:dyDescent="0.45">
       <c r="A19" s="8">
         <v>3030</v>
       </c>
@@ -17059,7 +17199,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:21" ht="34" x14ac:dyDescent="0.45">
       <c r="A20" s="8">
         <v>3040</v>
       </c>
@@ -17127,7 +17267,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:21" ht="34" x14ac:dyDescent="0.45">
       <c r="A21" s="8">
         <v>3050</v>
       </c>
@@ -17187,7 +17327,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A22" s="8">
         <v>3060</v>
       </c>
@@ -17247,7 +17387,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:21" ht="34" x14ac:dyDescent="0.45">
       <c r="A23" s="8">
         <v>3070</v>
       </c>
@@ -17307,7 +17447,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A24" s="10">
         <v>4010</v>
       </c>
@@ -17337,34 +17477,34 @@
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
       <c r="M24" s="10"/>
-      <c r="N24" s="144"/>
-      <c r="O24" s="144"/>
-      <c r="P24" s="144" t="str">
+      <c r="N24" s="132"/>
+      <c r="O24" s="132"/>
+      <c r="P24" s="132" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q24" s="144" t="str">
+      <c r="Q24" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R24" s="144" t="str">
+      <c r="R24" s="132" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="S24" s="144" t="str">
+      <c r="S24" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T24" s="144" t="str">
+      <c r="T24" s="132" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U24" s="144" t="str">
+      <c r="U24" s="132" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:21" ht="34" x14ac:dyDescent="0.45">
       <c r="A25" s="10">
         <v>4020</v>
       </c>
@@ -17398,36 +17538,36 @@
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
       <c r="M25" s="10"/>
-      <c r="N25" s="144">
+      <c r="N25" s="132">
         <v>0.8</v>
       </c>
-      <c r="O25" s="144"/>
-      <c r="P25" s="144">
+      <c r="O25" s="132"/>
+      <c r="P25" s="132">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q25" s="144" t="str">
+      <c r="Q25" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R25" s="144">
+      <c r="R25" s="132">
         <f t="shared" si="3"/>
         <v>1.2</v>
       </c>
-      <c r="S25" s="144" t="str">
+      <c r="S25" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T25" s="144">
+      <c r="T25" s="132">
         <f t="shared" si="5"/>
         <v>1.4</v>
       </c>
-      <c r="U25" s="144" t="str">
+      <c r="U25" s="132" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:21" ht="34" x14ac:dyDescent="0.45">
       <c r="A26" s="10">
         <v>4030</v>
       </c>
@@ -17457,34 +17597,34 @@
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
       <c r="M26" s="10"/>
-      <c r="N26" s="144"/>
-      <c r="O26" s="144"/>
-      <c r="P26" s="144" t="str">
+      <c r="N26" s="132"/>
+      <c r="O26" s="132"/>
+      <c r="P26" s="132" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q26" s="144" t="str">
+      <c r="Q26" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R26" s="144" t="str">
+      <c r="R26" s="132" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="S26" s="144" t="str">
+      <c r="S26" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T26" s="144" t="str">
+      <c r="T26" s="132" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U26" s="144" t="str">
+      <c r="U26" s="132" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A27" s="10">
         <v>4040</v>
       </c>
@@ -17518,36 +17658,36 @@
       <c r="K27" s="10"/>
       <c r="L27" s="10"/>
       <c r="M27" s="10"/>
-      <c r="N27" s="144">
+      <c r="N27" s="132">
         <v>1</v>
       </c>
-      <c r="O27" s="144"/>
-      <c r="P27" s="144">
+      <c r="O27" s="132"/>
+      <c r="P27" s="132">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
-      <c r="Q27" s="144" t="str">
+      <c r="Q27" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R27" s="144">
+      <c r="R27" s="132">
         <f t="shared" si="3"/>
         <v>1.4</v>
       </c>
-      <c r="S27" s="144" t="str">
+      <c r="S27" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T27" s="144">
+      <c r="T27" s="132">
         <f t="shared" si="5"/>
         <v>1.7</v>
       </c>
-      <c r="U27" s="144" t="str">
+      <c r="U27" s="132" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A28" s="10">
         <v>4050</v>
       </c>
@@ -17577,34 +17717,34 @@
       <c r="K28" s="10"/>
       <c r="L28" s="10"/>
       <c r="M28" s="10"/>
-      <c r="N28" s="144"/>
-      <c r="O28" s="144"/>
-      <c r="P28" s="144" t="str">
+      <c r="N28" s="132"/>
+      <c r="O28" s="132"/>
+      <c r="P28" s="132" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q28" s="144" t="str">
+      <c r="Q28" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R28" s="144" t="str">
+      <c r="R28" s="132" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="S28" s="144" t="str">
+      <c r="S28" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T28" s="144" t="str">
+      <c r="T28" s="132" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U28" s="144" t="str">
+      <c r="U28" s="132" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A29" s="10">
         <v>4060</v>
       </c>
@@ -17638,36 +17778,36 @@
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
       <c r="M29" s="10"/>
-      <c r="N29" s="144">
+      <c r="N29" s="132">
         <v>0.5</v>
       </c>
-      <c r="O29" s="144"/>
-      <c r="P29" s="144">
+      <c r="O29" s="132"/>
+      <c r="P29" s="132">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="Q29" s="144" t="str">
+      <c r="Q29" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R29" s="144">
+      <c r="R29" s="132">
         <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
-      <c r="S29" s="144" t="str">
+      <c r="S29" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T29" s="144">
+      <c r="T29" s="132">
         <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
-      <c r="U29" s="144" t="str">
+      <c r="U29" s="132" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A30" s="10">
         <v>4070</v>
       </c>
@@ -17697,34 +17837,34 @@
       <c r="K30" s="10"/>
       <c r="L30" s="10"/>
       <c r="M30" s="10"/>
-      <c r="N30" s="144"/>
-      <c r="O30" s="144"/>
-      <c r="P30" s="144" t="str">
+      <c r="N30" s="132"/>
+      <c r="O30" s="132"/>
+      <c r="P30" s="132" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q30" s="144" t="str">
+      <c r="Q30" s="132" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="R30" s="144" t="str">
+      <c r="R30" s="132" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="S30" s="144" t="str">
+      <c r="S30" s="132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T30" s="144" t="str">
+      <c r="T30" s="132" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U30" s="144" t="str">
+      <c r="U30" s="132" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="50.65" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:21" ht="51" x14ac:dyDescent="0.45">
       <c r="A31" s="8">
         <v>5010</v>
       </c>
@@ -17792,7 +17932,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A32" s="8">
         <v>5020</v>
       </c>
@@ -17852,7 +17992,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:21" ht="34" x14ac:dyDescent="0.45">
       <c r="A33" s="8">
         <v>5030</v>
       </c>
@@ -17892,7 +18032,7 @@
       <c r="N33" s="33">
         <v>1.2</v>
       </c>
-      <c r="O33" s="147">
+      <c r="O33" s="135">
         <f>N33*50%</f>
         <v>0.6</v>
       </c>
@@ -17921,7 +18061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:21" ht="34" x14ac:dyDescent="0.45">
       <c r="A34" s="8">
         <v>5040</v>
       </c>
@@ -17989,7 +18129,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:21" ht="34" x14ac:dyDescent="0.45">
       <c r="A35" s="8">
         <v>5050</v>
       </c>
@@ -18049,7 +18189,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="54" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:21" ht="54" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="8">
         <v>5060</v>
       </c>
@@ -18109,7 +18249,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:21" ht="34" x14ac:dyDescent="0.45">
       <c r="A37" s="8">
         <v>5070</v>
       </c>
@@ -18189,26 +18329,26 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7013FEB1-D337-4EB8-BD9B-6CA8F5E6412F}">
   <dimension ref="A2:H3"/>
-  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="8.5625" style="1"/>
+    <col min="1" max="16384" width="8.58203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="34.9" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:8" ht="36" x14ac:dyDescent="0.45">
       <c r="A2" s="14" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="321" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B3" s="134" t="s">
+    <row r="3" spans="1:8" ht="321" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="136" t="s">
         <v>592</v>
       </c>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
     </row>
   </sheetData>
   <mergeCells count="1">
